--- a/models_multiW_5k.xlsx
+++ b/models_multiW_5k.xlsx
@@ -8,26 +8,38 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Semester\SemesterVII\thesis_1228\lab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E80A4DC5-1BF8-4EA1-8593-9EBAEA0CEFF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F941EC91-9CE4-448D-8860-377C02F1276B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="578" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="481" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distance" sheetId="1" r:id="rId1"/>
-    <sheet name="all" sheetId="2" r:id="rId2"/>
-    <sheet name="Queen" sheetId="3" r:id="rId3"/>
+    <sheet name="K5" sheetId="6" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
+    <sheet name="all" sheetId="2" r:id="rId4"/>
+    <sheet name="Queen" sheetId="3" r:id="rId5"/>
+    <sheet name="example" sheetId="5" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="998">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2555" uniqueCount="1356">
   <si>
     <t>CONSTANT</t>
   </si>
@@ -2703,31 +2715,7 @@
     <t>0.863</t>
   </si>
   <si>
-    <t>0.070</t>
-  </si>
-  <si>
     <t>0.038</t>
-  </si>
-  <si>
-    <t>-0.009</t>
-  </si>
-  <si>
-    <t>0.104</t>
-  </si>
-  <si>
-    <t>0.190</t>
-  </si>
-  <si>
-    <t>0.323</t>
-  </si>
-  <si>
-    <t>0.339</t>
-  </si>
-  <si>
-    <t>0.389</t>
-  </si>
-  <si>
-    <t>0.388</t>
   </si>
   <si>
     <t>-228.813</t>
@@ -3545,6 +3533,1276 @@
   </si>
   <si>
     <t>Likelihood Ratio (LR)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.238
+(1.902)</t>
+  </si>
+  <si>
+    <t>-5.518
+(3.537)</t>
+  </si>
+  <si>
+    <t>0.701
+(1.070)</t>
+  </si>
+  <si>
+    <t>0.630
+(0.825)</t>
+  </si>
+  <si>
+    <t>-0.073
+(0.957)</t>
+  </si>
+  <si>
+    <t>0.069
+(0.992)</t>
+  </si>
+  <si>
+    <t>0.310
+(0.985)</t>
+  </si>
+  <si>
+    <t>0.523
+(1.007)</t>
+  </si>
+  <si>
+    <t>0.319
+(1.031)</t>
+  </si>
+  <si>
+    <t>0.203
+(1.008)</t>
+  </si>
+  <si>
+    <t>0.303
+(1.023)</t>
+  </si>
+  <si>
+    <t>0.007
+(0.154)</t>
+  </si>
+  <si>
+    <t>0.175
+(0.137)</t>
+  </si>
+  <si>
+    <t>0.092
+(0.142)</t>
+  </si>
+  <si>
+    <t>0.061
+(0.147)</t>
+  </si>
+  <si>
+    <t>0.063
+(0.149)</t>
+  </si>
+  <si>
+    <t>0.040
+(0.150)</t>
+  </si>
+  <si>
+    <t>0.076
+(0.149)</t>
+  </si>
+  <si>
+    <t>0.077
+(0.146)</t>
+  </si>
+  <si>
+    <t>0.111
+(0.148)</t>
+  </si>
+  <si>
+    <t>-0.008
+(0.152)</t>
+  </si>
+  <si>
+    <t>-0.116
+(0.140)</t>
+  </si>
+  <si>
+    <t>-0.056
+(0.147)</t>
+  </si>
+  <si>
+    <t>-0.068
+(0.153)</t>
+  </si>
+  <si>
+    <t>-0.087
+(0.156)</t>
+  </si>
+  <si>
+    <t>-0.031
+(0.155)</t>
+  </si>
+  <si>
+    <t>0.002
+(0.158)</t>
+  </si>
+  <si>
+    <t>0.008
+(0.151)</t>
+  </si>
+  <si>
+    <t>0.002
+(0.152)</t>
+  </si>
+  <si>
+    <t>0.087
+(0.200)</t>
+  </si>
+  <si>
+    <t>0.118
+(0.200)</t>
+  </si>
+  <si>
+    <t>0.087
+(0.211)</t>
+  </si>
+  <si>
+    <t>0.004
+(0.212)</t>
+  </si>
+  <si>
+    <t>-0.034
+(0.209)</t>
+  </si>
+  <si>
+    <t>-0.019
+(0.209)</t>
+  </si>
+  <si>
+    <t>-0.022
+(0.210)</t>
+  </si>
+  <si>
+    <t>-0.038
+(0.210)</t>
+  </si>
+  <si>
+    <t>-0.028
+(0.209)</t>
+  </si>
+  <si>
+    <t>-1.648
+(1.453)</t>
+  </si>
+  <si>
+    <t>-2.425
+(1.583)</t>
+  </si>
+  <si>
+    <t>-0.669
+(1.106)</t>
+  </si>
+  <si>
+    <t>-1.019
+(1.229)</t>
+  </si>
+  <si>
+    <t>-1.380
+(1.293)</t>
+  </si>
+  <si>
+    <t>-1.535
+(1.344)</t>
+  </si>
+  <si>
+    <t>-1.340
+(1.442)</t>
+  </si>
+  <si>
+    <t>-1.277
+(1.427)</t>
+  </si>
+  <si>
+    <t>-1.742
+(1.469)</t>
+  </si>
+  <si>
+    <t>-0.307
+(0.244)</t>
+  </si>
+  <si>
+    <t>0.179
+(0.194)</t>
+  </si>
+  <si>
+    <t>0.198
+(0.208)</t>
+  </si>
+  <si>
+    <t>0.193
+(0.228)</t>
+  </si>
+  <si>
+    <t>0.248
+(0.250)</t>
+  </si>
+  <si>
+    <t>0.198
+(0.264)</t>
+  </si>
+  <si>
+    <t>0.220
+(0.270)</t>
+  </si>
+  <si>
+    <t>0.035
+(0.281)</t>
+  </si>
+  <si>
+    <t>-0.343
+(0.254)</t>
+  </si>
+  <si>
+    <t>0.397
+(0.269)</t>
+  </si>
+  <si>
+    <t>-0.116
+(0.178)</t>
+  </si>
+  <si>
+    <t>-0.089
+(0.206)</t>
+  </si>
+  <si>
+    <t>0.005
+(0.235)</t>
+  </si>
+  <si>
+    <t>-0.084
+(0.247)</t>
+  </si>
+  <si>
+    <t>-0.161
+(0.259)</t>
+  </si>
+  <si>
+    <t>-0.250
+(0.254)</t>
+  </si>
+  <si>
+    <t>-0.226
+(0.266)</t>
+  </si>
+  <si>
+    <t>-0.017
+(0.195)</t>
+  </si>
+  <si>
+    <t>0.417
+(0.359)</t>
+  </si>
+  <si>
+    <t>0.489
+(0.397)</t>
+  </si>
+  <si>
+    <t>0.616
+(0.431)</t>
+  </si>
+  <si>
+    <t>0.601
+(0.446)</t>
+  </si>
+  <si>
+    <t>0.139
+(0.283)</t>
+  </si>
+  <si>
+    <t>0.114
+(0.266)</t>
+  </si>
+  <si>
+    <t>0.064
+(0.196)</t>
+  </si>
+  <si>
+    <t>-0.008
+(0.216)</t>
+  </si>
+  <si>
+    <t>0.028
+(0.224)</t>
+  </si>
+  <si>
+    <t>0.023
+(0.242)</t>
+  </si>
+  <si>
+    <t>0.141
+(0.250)</t>
+  </si>
+  <si>
+    <t>0.103
+(0.252)</t>
+  </si>
+  <si>
+    <t>0.140
+(0.263)</t>
+  </si>
+  <si>
+    <t>0.444
+(1.175)</t>
+  </si>
+  <si>
+    <t>-0.042
+(1.025)</t>
+  </si>
+  <si>
+    <t>-0.146
+(0.963)</t>
+  </si>
+  <si>
+    <t>0.359
+(1.078)</t>
+  </si>
+  <si>
+    <t>0.711
+(1.153)</t>
+  </si>
+  <si>
+    <t>1.471
+(1.191)</t>
+  </si>
+  <si>
+    <t>1.203
+(1.269)</t>
+  </si>
+  <si>
+    <t>1.101
+(1.293)</t>
+  </si>
+  <si>
+    <t>0.981
+(1.356)</t>
+  </si>
+  <si>
+    <t>0.067
+[0.162]</t>
+  </si>
+  <si>
+    <t>0.183
+[0.003]</t>
+  </si>
+  <si>
+    <t>0.142
+[0.005]</t>
+  </si>
+  <si>
+    <t>0.129
+[0.004]</t>
+  </si>
+  <si>
+    <t>0.144
+[0.000]</t>
+  </si>
+  <si>
+    <t>0.106
+[0.001]</t>
+  </si>
+  <si>
+    <t>0.078
+[0.010]</t>
+  </si>
+  <si>
+    <t>0.617</t>
+  </si>
+  <si>
+    <t>-236.778</t>
+  </si>
+  <si>
+    <t>-239.370</t>
+  </si>
+  <si>
+    <t>-239.985</t>
+  </si>
+  <si>
+    <t>-239.937</t>
+  </si>
+  <si>
+    <t>-239.456</t>
+  </si>
+  <si>
+    <t>-239.858</t>
+  </si>
+  <si>
+    <t>-240.198</t>
+  </si>
+  <si>
+    <t>-240.201</t>
+  </si>
+  <si>
+    <t>-240.462</t>
+  </si>
+  <si>
+    <t>499.556</t>
+  </si>
+  <si>
+    <t>504.741</t>
+  </si>
+  <si>
+    <t>505.971</t>
+  </si>
+  <si>
+    <t>505.874</t>
+  </si>
+  <si>
+    <t>504.912</t>
+  </si>
+  <si>
+    <t>505.716</t>
+  </si>
+  <si>
+    <t>506.396</t>
+  </si>
+  <si>
+    <t>506.401</t>
+  </si>
+  <si>
+    <t>506.925</t>
+  </si>
+  <si>
+    <t>542.304</t>
+  </si>
+  <si>
+    <t>547.488</t>
+  </si>
+  <si>
+    <t>548.718</t>
+  </si>
+  <si>
+    <t>548.622</t>
+  </si>
+  <si>
+    <t>547.660</t>
+  </si>
+  <si>
+    <t>548.464</t>
+  </si>
+  <si>
+    <t>549.144</t>
+  </si>
+  <si>
+    <t>549.149</t>
+  </si>
+  <si>
+    <t>549.672</t>
+  </si>
+  <si>
+    <t>13.885</t>
+  </si>
+  <si>
+    <t>8.700</t>
+  </si>
+  <si>
+    <t>7.470</t>
+  </si>
+  <si>
+    <t>7.567</t>
+  </si>
+  <si>
+    <t>8.529</t>
+  </si>
+  <si>
+    <t>7.725</t>
+  </si>
+  <si>
+    <t>7.045</t>
+  </si>
+  <si>
+    <t>7.040</t>
+  </si>
+  <si>
+    <t>6.517</t>
+  </si>
+  <si>
+    <t>SLX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-8.941***
+(2.854)</t>
+  </si>
+  <si>
+    <t>-6.363***
+(2.440)</t>
+  </si>
+  <si>
+    <t>-6.360**
+(2.642)</t>
+  </si>
+  <si>
+    <t>-6.195**
+(2.889)</t>
+  </si>
+  <si>
+    <t>-5.098*
+(2.946)</t>
+  </si>
+  <si>
+    <t>-5.742*
+(3.121)</t>
+  </si>
+  <si>
+    <t>-6.418*
+(3.369)</t>
+  </si>
+  <si>
+    <t>0.539***
+(0.174)</t>
+  </si>
+  <si>
+    <t>0.538***
+(0.138)</t>
+  </si>
+  <si>
+    <t>0.526***
+(0.157)</t>
+  </si>
+  <si>
+    <t>0.588***
+(0.162)</t>
+  </si>
+  <si>
+    <t>0.576***
+(0.163)</t>
+  </si>
+  <si>
+    <t>0.592***
+(0.166)</t>
+  </si>
+  <si>
+    <t>0.530***
+(0.166)</t>
+  </si>
+  <si>
+    <t>0.552***
+(0.162)</t>
+  </si>
+  <si>
+    <t>0.539***
+(0.164)</t>
+  </si>
+  <si>
+    <t>-3.413***
+(0.837)</t>
+  </si>
+  <si>
+    <t>-3.127***
+(0.659)</t>
+  </si>
+  <si>
+    <t>-3.202***
+(0.757)</t>
+  </si>
+  <si>
+    <t>-3.584***
+(0.784)</t>
+  </si>
+  <si>
+    <t>-3.660***
+(0.774)</t>
+  </si>
+  <si>
+    <t>-3.900***
+(0.772)</t>
+  </si>
+  <si>
+    <t>-3.790***
+(0.777)</t>
+  </si>
+  <si>
+    <t>-3.800***
+(0.771)</t>
+  </si>
+  <si>
+    <t>-3.905***
+(0.779)</t>
+  </si>
+  <si>
+    <t>0.431*
+(0.251)</t>
+  </si>
+  <si>
+    <t>0.705**
+(0.351)</t>
+  </si>
+  <si>
+    <t>0.534**
+(0.264)</t>
+  </si>
+  <si>
+    <t>0.619**
+(0.304)</t>
+  </si>
+  <si>
+    <t>0.578*
+(0.348)</t>
+  </si>
+  <si>
+    <t>-8.941***</t>
+  </si>
+  <si>
+    <t>0.539***</t>
+  </si>
+  <si>
+    <t>-3.413***</t>
+  </si>
+  <si>
+    <t>0.431*</t>
+  </si>
+  <si>
+    <t>0.705**</t>
+  </si>
+  <si>
+    <t>(2.678)</t>
+  </si>
+  <si>
+    <t>(3.689)</t>
+  </si>
+  <si>
+    <t>(1.494)</t>
+  </si>
+  <si>
+    <t>-1.793</t>
+  </si>
+  <si>
+    <t>(1.593)</t>
+  </si>
+  <si>
+    <t>0.592</t>
+  </si>
+  <si>
+    <t>(1.665)</t>
+  </si>
+  <si>
+    <t>(1.567)</t>
+  </si>
+  <si>
+    <t>0.621</t>
+  </si>
+  <si>
+    <t>(0.981)</t>
+  </si>
+  <si>
+    <t>0.423</t>
+  </si>
+  <si>
+    <t>(0.914)</t>
+  </si>
+  <si>
+    <t>0.116</t>
+  </si>
+  <si>
+    <t>(0.589)</t>
+  </si>
+  <si>
+    <t>-0.274</t>
+  </si>
+  <si>
+    <t>(0.642)</t>
+  </si>
+  <si>
+    <t>0.153</t>
+  </si>
+  <si>
+    <t>(0.774)</t>
+  </si>
+  <si>
+    <t>0.212</t>
+  </si>
+  <si>
+    <t>(0.625)</t>
+  </si>
+  <si>
+    <t>-0.020</t>
+  </si>
+  <si>
+    <t>(0.141)</t>
+  </si>
+  <si>
+    <t>0.024</t>
+  </si>
+  <si>
+    <t>(0.135)</t>
+  </si>
+  <si>
+    <t>0.086</t>
+  </si>
+  <si>
+    <t>(0.112)</t>
+  </si>
+  <si>
+    <t>0.142</t>
+  </si>
+  <si>
+    <t>(0.122)</t>
+  </si>
+  <si>
+    <t>0.025</t>
+  </si>
+  <si>
+    <t>(0.129)</t>
+  </si>
+  <si>
+    <t>0.065</t>
+  </si>
+  <si>
+    <t>(0.115)</t>
+  </si>
+  <si>
+    <t>-0.006</t>
+  </si>
+  <si>
+    <t>(0.139)</t>
+  </si>
+  <si>
+    <t>(0.133)</t>
+  </si>
+  <si>
+    <t>-0.032</t>
+  </si>
+  <si>
+    <t>-0.035</t>
+  </si>
+  <si>
+    <t>(0.125)</t>
+  </si>
+  <si>
+    <t>-0.003</t>
+  </si>
+  <si>
+    <t>(0.134)</t>
+  </si>
+  <si>
+    <t>-0.025</t>
+  </si>
+  <si>
+    <t>(0.117)</t>
+  </si>
+  <si>
+    <t>0.047</t>
+  </si>
+  <si>
+    <t>(0.184)</t>
+  </si>
+  <si>
+    <t>0.113</t>
+  </si>
+  <si>
+    <t>(0.182)</t>
+  </si>
+  <si>
+    <t>0.217</t>
+  </si>
+  <si>
+    <t>(0.156)</t>
+  </si>
+  <si>
+    <t>(0.169)</t>
+  </si>
+  <si>
+    <t>0.008</t>
+  </si>
+  <si>
+    <t>(0.165)</t>
+  </si>
+  <si>
+    <t>0.210</t>
+  </si>
+  <si>
+    <t>(0.157)</t>
+  </si>
+  <si>
+    <t>(0.159)</t>
+  </si>
+  <si>
+    <t>(0.151)</t>
+  </si>
+  <si>
+    <t>(0.131)</t>
+  </si>
+  <si>
+    <t>(0.144)</t>
+  </si>
+  <si>
+    <t>(0.767)</t>
+  </si>
+  <si>
+    <t>(0.744)</t>
+  </si>
+  <si>
+    <t>(0.559)</t>
+  </si>
+  <si>
+    <t>(0.573)</t>
+  </si>
+  <si>
+    <t>(0.639)</t>
+  </si>
+  <si>
+    <t>(0.651)</t>
+  </si>
+  <si>
+    <t>-1.044</t>
+  </si>
+  <si>
+    <t>(1.332)</t>
+  </si>
+  <si>
+    <t>-0.556</t>
+  </si>
+  <si>
+    <t>(1.467)</t>
+  </si>
+  <si>
+    <t>0.345</t>
+  </si>
+  <si>
+    <t>(0.231)</t>
+  </si>
+  <si>
+    <t>(0.272)</t>
+  </si>
+  <si>
+    <t>-0.235</t>
+  </si>
+  <si>
+    <t>(0.233)</t>
+  </si>
+  <si>
+    <t>-0.270</t>
+  </si>
+  <si>
+    <t>(0.273)</t>
+  </si>
+  <si>
+    <t>0.499</t>
+  </si>
+  <si>
+    <t>(0.324)</t>
+  </si>
+  <si>
+    <t>0.577</t>
+  </si>
+  <si>
+    <t>(0.381)</t>
+  </si>
+  <si>
+    <t>-0.089</t>
+  </si>
+  <si>
+    <t>(0.265)</t>
+  </si>
+  <si>
+    <t>0.195</t>
+  </si>
+  <si>
+    <t>(0.303)</t>
+  </si>
+  <si>
+    <t>1.466</t>
+  </si>
+  <si>
+    <t>(1.113)</t>
+  </si>
+  <si>
+    <t>-0.065</t>
+  </si>
+  <si>
+    <t>(1.273)</t>
+  </si>
+  <si>
+    <t>(0.091)</t>
+  </si>
+  <si>
+    <t>(0.079)</t>
+  </si>
+  <si>
+    <t>(0.178)</t>
+  </si>
+  <si>
+    <t>(0.090)</t>
+  </si>
+  <si>
+    <t>(0.086)</t>
+  </si>
+  <si>
+    <t>0.035</t>
+  </si>
+  <si>
+    <t>0.173</t>
+  </si>
+  <si>
+    <t>0.044</t>
+  </si>
+  <si>
+    <t>0.199</t>
+  </si>
+  <si>
+    <t>0.029</t>
+  </si>
+  <si>
+    <t>(-2.854)</t>
+  </si>
+  <si>
+    <t>(-1.07)</t>
+  </si>
+  <si>
+    <t>(-0.154)</t>
+  </si>
+  <si>
+    <t>(-0.152)</t>
+  </si>
+  <si>
+    <t>(-0.2)</t>
+  </si>
+  <si>
+    <t>(-0.174)</t>
+  </si>
+  <si>
+    <t>(-0.837)</t>
+  </si>
+  <si>
+    <t>(-1.453)</t>
+  </si>
+  <si>
+    <t>(-0.251)</t>
+  </si>
+  <si>
+    <t>(-0.254)</t>
+  </si>
+  <si>
+    <t>(-0.351)</t>
+  </si>
+  <si>
+    <t>(-0.283)</t>
+  </si>
+  <si>
+    <t>(-1.175)</t>
+  </si>
+  <si>
+    <t>([0.000])</t>
+  </si>
+  <si>
+    <t>Distance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OLS3</t>
+  </si>
+  <si>
+    <t>OLS4</t>
+  </si>
+  <si>
+    <t>OLS5</t>
+  </si>
+  <si>
+    <t>OLS6</t>
+  </si>
+  <si>
+    <t>OLS7</t>
+  </si>
+  <si>
+    <t>OLS8</t>
+  </si>
+  <si>
+    <t>OLS9</t>
+  </si>
+  <si>
+    <t>OLS10</t>
+  </si>
+  <si>
+    <t>OLS11</t>
+  </si>
+  <si>
+    <t>OLS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-2.931*
+(1.568)</t>
+  </si>
+  <si>
+    <t>0.212
+(0.626)</t>
+  </si>
+  <si>
+    <t>0.065
+(0.116)</t>
+  </si>
+  <si>
+    <t>-0.025
+(0.118)</t>
+  </si>
+  <si>
+    <t>0.210
+(0.158)</t>
+  </si>
+  <si>
+    <t>0.434***
+(0.130)</t>
+  </si>
+  <si>
+    <t>-1.981***
+(0.652)</t>
+  </si>
+  <si>
+    <t>0.499***
+(0.179)</t>
+  </si>
+  <si>
+    <t>0.029
+[0.423]</t>
+  </si>
+  <si>
+    <t>0.648</t>
+  </si>
+  <si>
+    <t>W_ln_access</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.087
+(0.055)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.070**
+(0.032)</t>
+  </si>
+  <si>
+    <t>0.038***
+(0.004)</t>
+  </si>
+  <si>
+    <t>-0.009
+(0.024)</t>
+  </si>
+  <si>
+    <t>0.104***
+(0.031)</t>
+  </si>
+  <si>
+    <t>0.190***
+(0.035)</t>
+  </si>
+  <si>
+    <t>0.323***
+(0.038)</t>
+  </si>
+  <si>
+    <t>0.339***
+(0.037)</t>
+  </si>
+  <si>
+    <t>0.389***
+(0.042)</t>
+  </si>
+  <si>
+    <t>0.388***
+(0.044)</t>
+  </si>
+  <si>
+    <t>0.289***
+(0.087)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.812***
+(0.106)</t>
+  </si>
+  <si>
+    <t>0.170
+(0.171)</t>
+  </si>
+  <si>
+    <t>0.615***
+(0.136)</t>
+  </si>
+  <si>
+    <t>0.675***
+(0.143)</t>
+  </si>
+  <si>
+    <t>0.734***
+(0.145)</t>
+  </si>
+  <si>
+    <t>0.760***
+(0.146)</t>
+  </si>
+  <si>
+    <t>0.791***
+(0.152)</t>
+  </si>
+  <si>
+    <t>0.799***
+(0.157)</t>
+  </si>
+  <si>
+    <t>0.794***
+(0.166)</t>
+  </si>
+  <si>
+    <t>0.031</t>
+  </si>
+  <si>
+    <t>0.483</t>
+  </si>
+  <si>
+    <t>0.498</t>
+  </si>
+  <si>
+    <t>0.523</t>
+  </si>
+  <si>
+    <t>0.517</t>
+  </si>
+  <si>
+    <t>0.500</t>
+  </si>
+  <si>
+    <t>0.468</t>
+  </si>
+  <si>
+    <t>0.037
+[0.319]</t>
+  </si>
+  <si>
+    <t>0.285
+[0.000]</t>
+  </si>
+  <si>
+    <t>-0.014
+[0.894]</t>
+  </si>
+  <si>
+    <t>-0.003
+[0.966]</t>
+  </si>
+  <si>
+    <t>0.021
+[0.569]</t>
+  </si>
+  <si>
+    <t>0.026
+[0.450]</t>
+  </si>
+  <si>
+    <t>0.039
+[0.248]</t>
+  </si>
+  <si>
+    <t>0.036
+[0.236]</t>
+  </si>
+  <si>
+    <t>0.021
+[0.426]</t>
+  </si>
+  <si>
+    <t>-264.485</t>
+  </si>
+  <si>
+    <t>-329.427</t>
+  </si>
+  <si>
+    <t>-286.669</t>
+  </si>
+  <si>
+    <t>-282.564</t>
+  </si>
+  <si>
+    <t>-277.160</t>
+  </si>
+  <si>
+    <t>-277.450</t>
+  </si>
+  <si>
+    <t>-277.627</t>
+  </si>
+  <si>
+    <t>-278.869</t>
+  </si>
+  <si>
+    <t>-282.785</t>
+  </si>
+  <si>
+    <t>532.970</t>
+  </si>
+  <si>
+    <t>662.854</t>
+  </si>
+  <si>
+    <t>577.338</t>
+  </si>
+  <si>
+    <t>569.127</t>
+  </si>
+  <si>
+    <t>558.321</t>
+  </si>
+  <si>
+    <t>558.900</t>
+  </si>
+  <si>
+    <t>559.253</t>
+  </si>
+  <si>
+    <t>561.738</t>
+  </si>
+  <si>
+    <t>569.570</t>
+  </si>
+  <si>
+    <t>539.547</t>
+  </si>
+  <si>
+    <t>669.431</t>
+  </si>
+  <si>
+    <t>583.915</t>
+  </si>
+  <si>
+    <t>575.704</t>
+  </si>
+  <si>
+    <t>564.897</t>
+  </si>
+  <si>
+    <t>565.477</t>
+  </si>
+  <si>
+    <t>565.830</t>
+  </si>
+  <si>
+    <t>568.315</t>
+  </si>
+  <si>
+    <t>576.147</t>
+  </si>
+  <si>
+    <t>FAR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统计量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>const</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rho</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3552,7 +4810,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3598,6 +4856,24 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="SimSun"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="SimSun"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3607,7 +4883,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -3659,11 +4935,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3671,33 +4958,123 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3717,6 +5094,138 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>245036</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>35857</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="113236" cy="172227"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2" name="文本框 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EDC2B2F-F0EF-7CA4-C385-41ED34205221}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7043271" y="4884269"/>
+              <a:ext cx="113236" cy="172227"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="zh-CN" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝜌</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2" name="文本框 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EDC2B2F-F0EF-7CA4-C385-41ED34205221}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7043271" y="4884269"/>
+              <a:ext cx="113236" cy="172227"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝜌</a:t>
+              </a:r>
+              <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -3808,6 +5317,290 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A86D4765-0A18-B449-E05F-00A361164CEF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="5168900"/>
+          <a:ext cx="69850" cy="234950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{908A8094-288F-FB19-CDF0-1CA6A93480CC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="4813300"/>
+          <a:ext cx="76200" cy="234950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>69850</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="图片 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EEDA8082-8046-C8BC-135C-8DC10D4DEAE1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="5168900"/>
+          <a:ext cx="69850" cy="234950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="图片 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF9689EB-8A40-A69E-7CBB-12B52182C20C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="4813300"/>
+          <a:ext cx="76200" cy="234950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>69850</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="图片 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3A97BD9-484D-D105-03C0-736C7D42A1A2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4126,232 +5919,1111 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:D31"/>
+  <dimension ref="A1:AC34"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="12.25" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.58203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.4140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.58203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.33203125" style="28" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="1" spans="1:29" ht="14.5" thickTop="1">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="28">
+      <c r="E1" t="s">
+        <v>988</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1277</v>
+      </c>
+      <c r="G1" t="s">
+        <v>618</v>
+      </c>
+      <c r="H1" t="s">
+        <v>709</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="M1" s="29" t="s">
+        <v>1267</v>
+      </c>
+      <c r="N1" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="O1" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="P1" s="29" t="s">
+        <v>988</v>
+      </c>
+      <c r="Q1" s="30" t="s">
+        <v>1277</v>
+      </c>
+      <c r="R1" s="30" t="s">
+        <v>618</v>
+      </c>
+      <c r="S1" s="30" t="s">
+        <v>709</v>
+      </c>
+      <c r="T1" s="31" t="s">
+        <v>1121</v>
+      </c>
+      <c r="V1" s="29" t="s">
+        <v>1267</v>
+      </c>
+      <c r="W1" s="29" t="s">
+        <v>1352</v>
+      </c>
+      <c r="X1" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y1" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z1" s="29" t="s">
+        <v>988</v>
+      </c>
+      <c r="AA1" s="30" t="s">
+        <v>618</v>
+      </c>
+      <c r="AB1" s="30" t="s">
+        <v>709</v>
+      </c>
+      <c r="AC1" s="31" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" ht="28">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="M2" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="N2" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="P2" s="33" t="s">
+        <v>861</v>
+      </c>
+      <c r="Q2" s="33" t="s">
+        <v>813</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="S2" s="33" t="s">
+        <v>620</v>
+      </c>
+      <c r="T2" s="33" t="s">
+        <v>990</v>
+      </c>
+      <c r="V2" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="W2" s="32"/>
+      <c r="X2" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y2" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z2" s="33" t="s">
+        <v>861</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="AB2" s="33" t="s">
+        <v>620</v>
+      </c>
+      <c r="AC2" s="33" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" ht="28">
       <c r="A3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="28">
+        <v>55</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>993</v>
+      </c>
+      <c r="M3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="N3" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="P3" s="33" t="s">
+        <v>870</v>
+      </c>
+      <c r="Q3" s="33" t="s">
+        <v>814</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="S3" s="33" t="s">
+        <v>629</v>
+      </c>
+      <c r="T3" s="33" t="s">
+        <v>993</v>
+      </c>
+      <c r="V3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="W3" s="32"/>
+      <c r="X3" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y3" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z3" s="33" t="s">
+        <v>870</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="AB3" s="33" t="s">
+        <v>629</v>
+      </c>
+      <c r="AC3" s="33" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" ht="28">
       <c r="A4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="28">
+        <v>56</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="M4" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="N4" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="P4" s="33" t="s">
+        <v>879</v>
+      </c>
+      <c r="Q4" s="33" t="s">
+        <v>815</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="S4" s="33" t="s">
+        <v>638</v>
+      </c>
+      <c r="T4" s="33" t="s">
+        <v>1002</v>
+      </c>
+      <c r="V4" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="W4" s="32"/>
+      <c r="X4" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y4" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z4" s="33" t="s">
+        <v>879</v>
+      </c>
+      <c r="AA4" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="AB4" s="33" t="s">
+        <v>638</v>
+      </c>
+      <c r="AC4" s="33" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" ht="28">
       <c r="A5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="28">
+        <v>57</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="M5" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="N5" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="O5" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="P5" s="33" t="s">
+        <v>887</v>
+      </c>
+      <c r="Q5" s="33" t="s">
+        <v>816</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="S5" s="33" t="s">
+        <v>647</v>
+      </c>
+      <c r="T5" s="33" t="s">
+        <v>1011</v>
+      </c>
+      <c r="V5" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="W5" s="32"/>
+      <c r="X5" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y5" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z5" s="33" t="s">
+        <v>887</v>
+      </c>
+      <c r="AA5" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="AB5" s="33" t="s">
+        <v>647</v>
+      </c>
+      <c r="AC5" s="33" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" ht="28">
       <c r="A6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="28">
+        <v>58</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="M6" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="N6" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="O6" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="P6" s="33" t="s">
+        <v>896</v>
+      </c>
+      <c r="Q6" s="33" t="s">
+        <v>817</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="S6" s="33" t="s">
+        <v>656</v>
+      </c>
+      <c r="T6" s="33" t="s">
+        <v>1020</v>
+      </c>
+      <c r="V6" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="W6" s="32"/>
+      <c r="X6" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y6" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z6" s="33" t="s">
+        <v>896</v>
+      </c>
+      <c r="AA6" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="AB6" s="33" t="s">
+        <v>656</v>
+      </c>
+      <c r="AC6" s="33" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" ht="28">
       <c r="A7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="28">
+        <v>59</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="M7" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="N7" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="O7" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="P7" s="33" t="s">
+        <v>905</v>
+      </c>
+      <c r="Q7" s="33" t="s">
+        <v>818</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="S7" s="33" t="s">
+        <v>665</v>
+      </c>
+      <c r="T7" s="33" t="s">
+        <v>1130</v>
+      </c>
+      <c r="V7" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="W7" s="32"/>
+      <c r="X7" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y7" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z7" s="33" t="s">
+        <v>905</v>
+      </c>
+      <c r="AA7" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="AB7" s="33" t="s">
+        <v>665</v>
+      </c>
+      <c r="AC7" s="33" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" ht="28">
       <c r="A8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="28">
+        <v>60</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>914</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="M8" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="N8" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="O8" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="P8" s="33" t="s">
+        <v>914</v>
+      </c>
+      <c r="Q8" s="33" t="s">
+        <v>819</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="S8" s="33" t="s">
+        <v>674</v>
+      </c>
+      <c r="T8" s="33" t="s">
+        <v>1139</v>
+      </c>
+      <c r="V8" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="W8" s="32"/>
+      <c r="X8" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y8" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z8" s="33" t="s">
+        <v>914</v>
+      </c>
+      <c r="AA8" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="AB8" s="33" t="s">
+        <v>674</v>
+      </c>
+      <c r="AC8" s="33" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" ht="28">
       <c r="A9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="28">
+        <v>61</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="M9" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="N9" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="O9" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="P9" s="34"/>
+      <c r="Q9" s="34"/>
+      <c r="R9" s="34"/>
+      <c r="S9" s="34"/>
+      <c r="T9" s="35" t="s">
+        <v>1029</v>
+      </c>
+      <c r="V9" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="W9" s="32"/>
+      <c r="X9" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y9" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z9" s="34"/>
+      <c r="AA9" s="34"/>
+      <c r="AB9" s="34"/>
+      <c r="AC9" s="35" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" ht="28">
       <c r="A10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="28">
+        <v>35</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>1037</v>
+      </c>
+      <c r="M10" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="N10" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="O10" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="P10" s="34"/>
+      <c r="Q10" s="34"/>
+      <c r="R10" s="34"/>
+      <c r="S10" s="34"/>
+      <c r="T10" s="35" t="s">
+        <v>1037</v>
+      </c>
+      <c r="V10" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="W10" s="32"/>
+      <c r="X10" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y10" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z10" s="34"/>
+      <c r="AA10" s="34"/>
+      <c r="AB10" s="34"/>
+      <c r="AC10" s="35" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" ht="28">
       <c r="A11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="28">
+        <v>36</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="M11" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="N11" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="O11" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="P11" s="34"/>
+      <c r="Q11" s="34"/>
+      <c r="R11" s="34"/>
+      <c r="S11" s="34"/>
+      <c r="T11" s="35" t="s">
+        <v>1046</v>
+      </c>
+      <c r="V11" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="W11" s="32"/>
+      <c r="X11" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y11" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z11" s="34"/>
+      <c r="AA11" s="34"/>
+      <c r="AB11" s="34"/>
+      <c r="AC11" s="35" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" ht="28">
       <c r="A12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="28">
+        <v>37</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="M12" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="N12" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="O12" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="P12" s="34"/>
+      <c r="Q12" s="34"/>
+      <c r="R12" s="34"/>
+      <c r="S12" s="34"/>
+      <c r="T12" s="35" t="s">
+        <v>1054</v>
+      </c>
+      <c r="V12" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="W12" s="32"/>
+      <c r="X12" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y12" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z12" s="34"/>
+      <c r="AA12" s="34"/>
+      <c r="AB12" s="34"/>
+      <c r="AC12" s="35" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" ht="28">
       <c r="A13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="28">
+        <v>38</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="M13" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="N13" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="O13" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="P13" s="34"/>
+      <c r="Q13" s="34"/>
+      <c r="R13" s="34"/>
+      <c r="S13" s="34"/>
+      <c r="T13" s="35" t="s">
+        <v>1060</v>
+      </c>
+      <c r="V13" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="W13" s="32"/>
+      <c r="X13" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y13" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z13" s="34"/>
+      <c r="AA13" s="34"/>
+      <c r="AB13" s="34"/>
+      <c r="AC13" s="35" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" ht="28">
       <c r="A14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="28">
-      <c r="A15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="M14" s="32" t="s">
         <v>12</v>
       </c>
+      <c r="N14" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="O14" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="P14" s="34"/>
+      <c r="Q14" s="34"/>
+      <c r="R14" s="34"/>
+      <c r="S14" s="34"/>
+      <c r="T14" s="35" t="s">
+        <v>1069</v>
+      </c>
+      <c r="V14" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="W14" s="32"/>
+      <c r="X14" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y14" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z14" s="34"/>
+      <c r="AA14" s="34"/>
+      <c r="AB14" s="34"/>
+      <c r="AC14" s="35" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" ht="28">
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>1301</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="28">
+        <v>40</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="M15" s="32" t="s">
+        <v>1288</v>
+      </c>
+      <c r="N15" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="O15" s="33"/>
+      <c r="P15" s="33"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="35" t="s">
+        <v>1289</v>
+      </c>
+      <c r="S15" s="33" t="s">
+        <v>683</v>
+      </c>
+      <c r="T15" s="33"/>
+      <c r="V15" s="32" t="s">
+        <v>1288</v>
+      </c>
+      <c r="W15" s="32" t="s">
+        <v>1301</v>
+      </c>
+      <c r="X15" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y15" s="33"/>
+      <c r="Z15" s="33"/>
+      <c r="AA15" s="35" t="s">
+        <v>1289</v>
+      </c>
+      <c r="AB15" s="33" t="s">
+        <v>683</v>
+      </c>
+      <c r="AC15" s="33"/>
+    </row>
+    <row r="16" spans="1:29" ht="28">
       <c r="A16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="28">
+      <c r="E16" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="M16" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="N16" s="33"/>
+      <c r="O16" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="P16" s="33" t="s">
+        <v>923</v>
+      </c>
+      <c r="Q16" s="34"/>
+      <c r="R16" s="3"/>
+      <c r="S16" s="33" t="s">
+        <v>746</v>
+      </c>
+      <c r="T16" s="33"/>
+      <c r="V16" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="W16" s="32"/>
+      <c r="X16" s="33"/>
+      <c r="Y16" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z16" s="33" t="s">
+        <v>923</v>
+      </c>
+      <c r="AA16" s="3"/>
+      <c r="AB16" s="33" t="s">
+        <v>1291</v>
+      </c>
+      <c r="AC16" s="33"/>
+    </row>
+    <row r="17" spans="1:29" ht="28">
       <c r="A17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="28">
+      <c r="E17" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="M17" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="N17" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="O17" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="P17" s="33" t="s">
+        <v>932</v>
+      </c>
+      <c r="Q17" s="34"/>
+      <c r="R17" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="S17" s="33" t="s">
+        <v>692</v>
+      </c>
+      <c r="T17" s="33" t="s">
+        <v>1077</v>
+      </c>
+      <c r="V17" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="W17" s="32" t="s">
+        <v>1317</v>
+      </c>
+      <c r="X17" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y17" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z17" s="33" t="s">
+        <v>932</v>
+      </c>
+      <c r="AA17" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="AB17" s="33" t="s">
+        <v>692</v>
+      </c>
+      <c r="AC17" s="33" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" ht="14.5" thickBot="1">
       <c r="A18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="28">
+      <c r="E18" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="M18" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="N18" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="O18" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="P18" s="37" t="s">
+        <v>941</v>
+      </c>
+      <c r="Q18" s="37"/>
+      <c r="R18" s="38" t="s">
+        <v>558</v>
+      </c>
+      <c r="S18" s="37" t="s">
+        <v>558</v>
+      </c>
+      <c r="T18" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="V18" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="W18" s="36" t="s">
+        <v>1309</v>
+      </c>
+      <c r="X18" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y18" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z18" s="37" t="s">
+        <v>941</v>
+      </c>
+      <c r="AA18" s="38" t="s">
+        <v>558</v>
+      </c>
+      <c r="AB18" s="37" t="s">
+        <v>558</v>
+      </c>
+      <c r="AC18" s="37" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" ht="28.5" thickTop="1">
       <c r="A19" s="2" t="s">
         <v>16</v>
       </c>
@@ -4362,10 +7034,19 @@
         <v>70</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="28">
+        <v>945</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" ht="28">
       <c r="A20" s="2" t="s">
         <v>17</v>
       </c>
@@ -4376,10 +7057,19 @@
         <v>71</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="28">
+        <v>954</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" ht="28">
       <c r="A21" s="2" t="s">
         <v>18</v>
       </c>
@@ -4390,10 +7080,19 @@
         <v>72</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
+        <v>963</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29">
       <c r="A22" s="2" t="s">
         <v>19</v>
       </c>
@@ -4404,10 +7103,17 @@
         <v>73</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+        <v>972</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" spans="1:29">
       <c r="A23" s="2" t="s">
         <v>20</v>
       </c>
@@ -4417,34 +7123,30 @@
       <c r="C23" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="F23" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29">
       <c r="B24" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D24" s="1"/>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="G24" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29">
       <c r="B25" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+      <c r="G25" s="1" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29">
       <c r="A26" s="2" t="s">
         <v>23</v>
       </c>
@@ -4452,38 +7154,83 @@
         <v>50</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+        <v>75</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29">
       <c r="A27" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" ht="42">
+      <c r="C27" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" ht="42">
       <c r="A28" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="D29" s="1" t="s">
+      <c r="C28" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>609</v>
       </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="D30" s="1" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="D31" s="1" t="s">
-        <v>600</v>
+      <c r="F28" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29">
+      <c r="E29" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29" ht="28">
+      <c r="E30" s="1" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29" ht="28">
+      <c r="E31" s="1" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29" ht="28">
+      <c r="E32" s="1" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="33" spans="4:8" ht="28">
+      <c r="E33" s="1" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="34" spans="4:8">
+      <c r="D34" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>1113</v>
       </c>
     </row>
   </sheetData>
@@ -4493,8 +7240,947 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC0710AF-BA80-4896-9DB8-04B96439F555}">
+  <dimension ref="A1:S34"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="11.58203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="14.5" thickTop="1">
+      <c r="B1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" t="s">
+        <v>988</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="F1" t="s">
+        <v>618</v>
+      </c>
+      <c r="G1" t="s">
+        <v>709</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="L1" s="19" t="s">
+        <v>1353</v>
+      </c>
+      <c r="M1" s="29" t="s">
+        <v>1352</v>
+      </c>
+      <c r="N1" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="O1" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="P1" s="29" t="s">
+        <v>988</v>
+      </c>
+      <c r="Q1" s="30" t="s">
+        <v>618</v>
+      </c>
+      <c r="R1" s="30" t="s">
+        <v>709</v>
+      </c>
+      <c r="S1" s="31" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="28">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>1126</v>
+      </c>
+      <c r="L2" s="32" t="s">
+        <v>1354</v>
+      </c>
+      <c r="M2" s="32"/>
+      <c r="N2" s="33" t="s">
+        <v>282</v>
+      </c>
+      <c r="O2" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="P2" s="33" t="s">
+        <v>865</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="R2" s="33" t="s">
+        <v>624</v>
+      </c>
+      <c r="S2" s="33" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="28">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="L3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3" s="32"/>
+      <c r="N3" s="33" t="s">
+        <v>290</v>
+      </c>
+      <c r="O3" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="P3" s="33" t="s">
+        <v>874</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="R3" s="33" t="s">
+        <v>633</v>
+      </c>
+      <c r="S3" s="33" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="28">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="L4" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="M4" s="32"/>
+      <c r="N4" s="33" t="s">
+        <v>298</v>
+      </c>
+      <c r="O4" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="P4" s="33" t="s">
+        <v>883</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="R4" s="33" t="s">
+        <v>642</v>
+      </c>
+      <c r="S4" s="33" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="28">
+      <c r="A5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="L5" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="M5" s="32"/>
+      <c r="N5" s="33" t="s">
+        <v>306</v>
+      </c>
+      <c r="O5" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="P5" s="33" t="s">
+        <v>891</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="R5" s="33" t="s">
+        <v>651</v>
+      </c>
+      <c r="S5" s="33" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="28">
+      <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="L6" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="M6" s="32"/>
+      <c r="N6" s="33" t="s">
+        <v>314</v>
+      </c>
+      <c r="O6" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="P6" s="33" t="s">
+        <v>900</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="R6" s="33" t="s">
+        <v>660</v>
+      </c>
+      <c r="S6" s="33" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="28">
+      <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="L7" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="M7" s="32"/>
+      <c r="N7" s="33" t="s">
+        <v>322</v>
+      </c>
+      <c r="O7" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="P7" s="33" t="s">
+        <v>909</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="R7" s="33" t="s">
+        <v>669</v>
+      </c>
+      <c r="S7" s="33" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="28">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="L8" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="M8" s="32"/>
+      <c r="N8" s="33" t="s">
+        <v>330</v>
+      </c>
+      <c r="O8" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="P8" s="33" t="s">
+        <v>918</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="R8" s="33" t="s">
+        <v>678</v>
+      </c>
+      <c r="S8" s="33" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="28">
+      <c r="A9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="L9" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="M9" s="32"/>
+      <c r="N9" s="33" t="s">
+        <v>338</v>
+      </c>
+      <c r="O9" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="P9" s="34"/>
+      <c r="Q9" s="34"/>
+      <c r="R9" s="34"/>
+      <c r="S9" s="35" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="28">
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="L10" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="32"/>
+      <c r="N10" s="33" t="s">
+        <v>346</v>
+      </c>
+      <c r="O10" s="33" t="s">
+        <v>157</v>
+      </c>
+      <c r="P10" s="34"/>
+      <c r="Q10" s="34"/>
+      <c r="R10" s="34"/>
+      <c r="S10" s="35" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="28">
+      <c r="A11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="L11" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="M11" s="32"/>
+      <c r="N11" s="33" t="s">
+        <v>354</v>
+      </c>
+      <c r="O11" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="P11" s="34"/>
+      <c r="Q11" s="34"/>
+      <c r="R11" s="34"/>
+      <c r="S11" s="35" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="28">
+      <c r="A12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L12" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="M12" s="32"/>
+      <c r="N12" s="33" t="s">
+        <v>362</v>
+      </c>
+      <c r="O12" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="P12" s="34"/>
+      <c r="Q12" s="34"/>
+      <c r="R12" s="34"/>
+      <c r="S12" s="35" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="28">
+      <c r="A13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="L13" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="M13" s="32"/>
+      <c r="N13" s="33" t="s">
+        <v>370</v>
+      </c>
+      <c r="O13" s="33" t="s">
+        <v>181</v>
+      </c>
+      <c r="P13" s="34"/>
+      <c r="Q13" s="34"/>
+      <c r="R13" s="34"/>
+      <c r="S13" s="35" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="28">
+      <c r="A14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="L14" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="M14" s="32"/>
+      <c r="N14" s="33" t="s">
+        <v>378</v>
+      </c>
+      <c r="O14" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="P14" s="34"/>
+      <c r="Q14" s="34"/>
+      <c r="R14" s="34"/>
+      <c r="S14" s="35" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="28">
+      <c r="A15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="F15" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="L15" s="32" t="s">
+        <v>1355</v>
+      </c>
+      <c r="M15" s="32" t="s">
+        <v>1305</v>
+      </c>
+      <c r="N15" s="33" t="s">
+        <v>386</v>
+      </c>
+      <c r="O15" s="33"/>
+      <c r="P15" s="33"/>
+      <c r="Q15" s="35" t="s">
+        <v>1299</v>
+      </c>
+      <c r="R15" s="33" t="s">
+        <v>687</v>
+      </c>
+      <c r="S15" s="33"/>
+    </row>
+    <row r="16" spans="1:19" ht="28">
+      <c r="A16" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="L16" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="M16" s="32"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="P16" s="33" t="s">
+        <v>927</v>
+      </c>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="33" t="s">
+        <v>1295</v>
+      </c>
+      <c r="S16" s="33"/>
+    </row>
+    <row r="17" spans="1:19" ht="28">
+      <c r="A17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="L17" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="M17" s="32" t="s">
+        <v>1321</v>
+      </c>
+      <c r="N17" s="33" t="s">
+        <v>394</v>
+      </c>
+      <c r="O17" s="33" t="s">
+        <v>206</v>
+      </c>
+      <c r="P17" s="33" t="s">
+        <v>936</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="R17" s="33" t="s">
+        <v>696</v>
+      </c>
+      <c r="S17" s="33" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="14.5" thickBot="1">
+      <c r="A18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="L18" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="M18" s="36" t="s">
+        <v>1313</v>
+      </c>
+      <c r="N18" s="37" t="s">
+        <v>401</v>
+      </c>
+      <c r="O18" s="37" t="s">
+        <v>213</v>
+      </c>
+      <c r="P18" s="37" t="s">
+        <v>943</v>
+      </c>
+      <c r="Q18" s="38" t="s">
+        <v>561</v>
+      </c>
+      <c r="R18" s="37" t="s">
+        <v>704</v>
+      </c>
+      <c r="S18" s="37" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="28.5" thickTop="1">
+      <c r="A19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="28">
+      <c r="A20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="28">
+      <c r="A21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
+      <c r="A22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" spans="1:19">
+      <c r="A23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19">
+      <c r="A24" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
+      <c r="A25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19">
+      <c r="A26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19">
+      <c r="A27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="42">
+      <c r="A28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="34" spans="4:8">
+      <c r="D34" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2E6FCE3-6139-4046-B8AC-8002B0F4F150}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E4E81B-B047-455C-B342-8FA95F48B51A}">
-  <dimension ref="A1:BM35"/>
+  <dimension ref="A1:CI35"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="11.58203125" bestFit="1" customWidth="1"/>
@@ -4502,29 +8188,223 @@
     <col min="23" max="23" width="11.58203125" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="11.75" customWidth="1"/>
     <col min="56" max="56" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="12.75" customWidth="1"/>
+    <col min="78" max="78" width="12.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:65">
+    <row r="1" spans="1:87">
+      <c r="A1" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="B1" s="1" t="s">
         <v>80</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1" t="s">
+        <v>78</v>
+      </c>
       <c r="M1" t="s">
         <v>78</v>
       </c>
+      <c r="N1" t="s">
+        <v>78</v>
+      </c>
+      <c r="O1" t="s">
+        <v>78</v>
+      </c>
+      <c r="P1" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>78</v>
+      </c>
+      <c r="R1" t="s">
+        <v>78</v>
+      </c>
+      <c r="S1" t="s">
+        <v>78</v>
+      </c>
+      <c r="T1" t="s">
+        <v>78</v>
+      </c>
+      <c r="U1" t="s">
+        <v>78</v>
+      </c>
+      <c r="W1" t="s">
+        <v>618</v>
+      </c>
       <c r="X1" t="s">
         <v>618</v>
       </c>
+      <c r="Y1" t="s">
+        <v>618</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>618</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>618</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>618</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>618</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>618</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>618</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>618</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>709</v>
+      </c>
       <c r="AI1" t="s">
         <v>709</v>
       </c>
+      <c r="AJ1" t="s">
+        <v>709</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>709</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>709</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>709</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>709</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>709</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>709</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>709</v>
+      </c>
+      <c r="AS1" s="2" t="s">
+        <v>811</v>
+      </c>
       <c r="AT1" s="2" t="s">
-        <v>819</v>
+        <v>1268</v>
+      </c>
+      <c r="AU1" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="AV1" s="2" t="s">
+        <v>1270</v>
+      </c>
+      <c r="AW1" s="2" t="s">
+        <v>1271</v>
+      </c>
+      <c r="AX1" s="2" t="s">
+        <v>1272</v>
+      </c>
+      <c r="AY1" s="2" t="s">
+        <v>1273</v>
+      </c>
+      <c r="AZ1" s="2" t="s">
+        <v>1274</v>
+      </c>
+      <c r="BA1" s="2" t="s">
+        <v>1275</v>
+      </c>
+      <c r="BB1" s="2" t="s">
+        <v>1276</v>
       </c>
       <c r="BD1" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="2" spans="1:65">
+        <v>988</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>988</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>988</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>988</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>988</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>988</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>988</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>988</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>988</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>988</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:87">
       <c r="B2" s="2" t="s">
         <v>81</v>
       </c>
@@ -4665,8 +8545,64 @@
       <c r="BM2" s="2" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="3" spans="1:65" ht="28">
+      <c r="BO2" s="1"/>
+      <c r="BP2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="BQ2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="BR2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="BS2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="BT2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="BU2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="BV2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="BW2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BX2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="BZ2" s="1"/>
+      <c r="CA2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="CB2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="CC2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="CD2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="CE2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="CF2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="CG2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="CH2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="CI2" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:87" ht="28">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -4788,43 +8724,73 @@
         <v>627</v>
       </c>
       <c r="AS3" s="2" t="s">
-        <v>820</v>
+        <v>812</v>
       </c>
       <c r="AT3" s="1" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="BD3" s="2" t="s">
-        <v>820</v>
+        <v>812</v>
       </c>
       <c r="BE3" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="BF3" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="BG3" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="BH3" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="BI3" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="BJ3" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="BK3" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="BL3" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="BM3" s="1" t="s">
         <v>868</v>
       </c>
-      <c r="BF3" s="1" t="s">
-        <v>869</v>
-      </c>
-      <c r="BG3" s="1" t="s">
-        <v>870</v>
-      </c>
-      <c r="BH3" s="1" t="s">
-        <v>871</v>
-      </c>
-      <c r="BI3" s="1" t="s">
-        <v>872</v>
-      </c>
-      <c r="BJ3" s="1" t="s">
-        <v>873</v>
-      </c>
-      <c r="BK3" s="1" t="s">
-        <v>874</v>
-      </c>
-      <c r="BL3" s="1" t="s">
-        <v>875</v>
-      </c>
-      <c r="BM3" s="1" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="4" spans="1:65" ht="28">
+      <c r="BO3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="BP3" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="BQ3" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="BR3" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="BS3" s="1" t="s">
+        <v>1124</v>
+      </c>
+      <c r="BT3" s="1" t="s">
+        <v>1125</v>
+      </c>
+      <c r="BU3" s="1" t="s">
+        <v>1126</v>
+      </c>
+      <c r="BV3" s="1" t="s">
+        <v>1127</v>
+      </c>
+      <c r="BW3" s="1" t="s">
+        <v>1128</v>
+      </c>
+      <c r="BX3" s="1" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="4" spans="1:87" ht="28">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -4949,40 +8915,70 @@
         <v>1</v>
       </c>
       <c r="AT4" s="1" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
       <c r="BD4" s="2" t="s">
         <v>1</v>
       </c>
       <c r="BE4" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="BF4" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="BG4" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="BH4" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="BI4" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="BJ4" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="BK4" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="BL4" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="BM4" s="1" t="s">
         <v>877</v>
       </c>
-      <c r="BF4" s="1" t="s">
-        <v>878</v>
-      </c>
-      <c r="BG4" s="1" t="s">
-        <v>879</v>
-      </c>
-      <c r="BH4" s="1" t="s">
-        <v>880</v>
-      </c>
-      <c r="BI4" s="1" t="s">
-        <v>881</v>
-      </c>
-      <c r="BJ4" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="BK4" s="1" t="s">
-        <v>883</v>
-      </c>
-      <c r="BL4" s="1" t="s">
-        <v>884</v>
-      </c>
-      <c r="BM4" s="1" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="5" spans="1:65" ht="28">
+      <c r="BO4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP4" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="BQ4" s="1" t="s">
+        <v>993</v>
+      </c>
+      <c r="BR4" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="BS4" s="1" t="s">
+        <v>995</v>
+      </c>
+      <c r="BT4" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="BU4" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="BV4" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="BW4" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="BX4" s="1" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:87" ht="28">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
@@ -5107,40 +9103,70 @@
         <v>2</v>
       </c>
       <c r="AT5" s="1" t="s">
-        <v>823</v>
+        <v>815</v>
       </c>
       <c r="BD5" s="2" t="s">
         <v>2</v>
       </c>
       <c r="BE5" s="1" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="BF5" s="1" t="s">
-        <v>887</v>
+        <v>879</v>
       </c>
       <c r="BG5" s="1" t="s">
-        <v>888</v>
+        <v>880</v>
       </c>
       <c r="BH5" s="1" t="s">
-        <v>889</v>
+        <v>881</v>
       </c>
       <c r="BI5" s="1" t="s">
-        <v>890</v>
+        <v>882</v>
       </c>
       <c r="BJ5" s="1" t="s">
-        <v>891</v>
+        <v>883</v>
       </c>
       <c r="BK5" s="1" t="s">
         <v>644</v>
       </c>
       <c r="BL5" s="1" t="s">
-        <v>892</v>
+        <v>884</v>
       </c>
       <c r="BM5" s="1" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="6" spans="1:65" ht="28">
+        <v>885</v>
+      </c>
+      <c r="BO5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BP5" s="1" t="s">
+        <v>1001</v>
+      </c>
+      <c r="BQ5" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="BR5" s="1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="BS5" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="BT5" s="1" t="s">
+        <v>1005</v>
+      </c>
+      <c r="BU5" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="BV5" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="BW5" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="BX5" s="1" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="6" spans="1:87" ht="28">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
@@ -5265,40 +9291,70 @@
         <v>3</v>
       </c>
       <c r="AT6" s="1" t="s">
-        <v>824</v>
+        <v>816</v>
       </c>
       <c r="BD6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="BE6" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="BF6" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="BG6" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="BH6" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="BI6" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="BJ6" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="BK6" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="BL6" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="BM6" s="1" t="s">
         <v>894</v>
       </c>
-      <c r="BF6" s="1" t="s">
-        <v>895</v>
-      </c>
-      <c r="BG6" s="1" t="s">
-        <v>896</v>
-      </c>
-      <c r="BH6" s="1" t="s">
-        <v>897</v>
-      </c>
-      <c r="BI6" s="1" t="s">
-        <v>898</v>
-      </c>
-      <c r="BJ6" s="1" t="s">
-        <v>899</v>
-      </c>
-      <c r="BK6" s="1" t="s">
-        <v>900</v>
-      </c>
-      <c r="BL6" s="1" t="s">
-        <v>901</v>
-      </c>
-      <c r="BM6" s="1" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="7" spans="1:65" ht="28">
+      <c r="BO6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="BP6" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="BQ6" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="BR6" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="BS6" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="BT6" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="BU6" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="BV6" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="BW6" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="BX6" s="1" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="7" spans="1:87" ht="28">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
@@ -5423,40 +9479,70 @@
         <v>4</v>
       </c>
       <c r="AT7" s="1" t="s">
-        <v>825</v>
+        <v>817</v>
       </c>
       <c r="BD7" s="2" t="s">
         <v>4</v>
       </c>
       <c r="BE7" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="BF7" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="BG7" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="BH7" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="BI7" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="BJ7" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="BK7" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="BL7" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="BM7" s="1" t="s">
         <v>903</v>
       </c>
-      <c r="BF7" s="1" t="s">
-        <v>904</v>
-      </c>
-      <c r="BG7" s="1" t="s">
-        <v>905</v>
-      </c>
-      <c r="BH7" s="1" t="s">
-        <v>906</v>
-      </c>
-      <c r="BI7" s="1" t="s">
-        <v>907</v>
-      </c>
-      <c r="BJ7" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="BK7" s="1" t="s">
-        <v>909</v>
-      </c>
-      <c r="BL7" s="1" t="s">
-        <v>910</v>
-      </c>
-      <c r="BM7" s="1" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="8" spans="1:65" ht="28">
+      <c r="BO7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP7" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="BQ7" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="BR7" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="BS7" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="BT7" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="BU7" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="BV7" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="BW7" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="BX7" s="1" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="8" spans="1:87" ht="28">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
@@ -5581,40 +9667,70 @@
         <v>5</v>
       </c>
       <c r="AT8" s="1" t="s">
-        <v>826</v>
+        <v>818</v>
       </c>
       <c r="BD8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="BE8" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="BF8" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="BG8" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="BH8" s="1" t="s">
+        <v>907</v>
+      </c>
+      <c r="BI8" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="BJ8" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="BK8" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="BL8" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="BM8" s="1" t="s">
         <v>912</v>
       </c>
-      <c r="BF8" s="1" t="s">
-        <v>913</v>
-      </c>
-      <c r="BG8" s="1" t="s">
-        <v>914</v>
-      </c>
-      <c r="BH8" s="1" t="s">
-        <v>915</v>
-      </c>
-      <c r="BI8" s="1" t="s">
-        <v>916</v>
-      </c>
-      <c r="BJ8" s="1" t="s">
-        <v>917</v>
-      </c>
-      <c r="BK8" s="1" t="s">
-        <v>918</v>
-      </c>
-      <c r="BL8" s="1" t="s">
-        <v>919</v>
-      </c>
-      <c r="BM8" s="1" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="9" spans="1:65" ht="28">
+      <c r="BO8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="BP8" s="1" t="s">
+        <v>1129</v>
+      </c>
+      <c r="BQ8" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="BR8" s="1" t="s">
+        <v>1131</v>
+      </c>
+      <c r="BS8" s="1" t="s">
+        <v>1132</v>
+      </c>
+      <c r="BT8" s="1" t="s">
+        <v>1133</v>
+      </c>
+      <c r="BU8" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="BV8" s="1" t="s">
+        <v>1135</v>
+      </c>
+      <c r="BW8" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="BX8" s="1" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="9" spans="1:87" ht="28">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
@@ -5739,40 +9855,70 @@
         <v>6</v>
       </c>
       <c r="AT9" s="1" t="s">
-        <v>827</v>
+        <v>819</v>
       </c>
       <c r="BD9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="BE9" s="1" t="s">
+        <v>913</v>
+      </c>
+      <c r="BF9" s="1" t="s">
+        <v>914</v>
+      </c>
+      <c r="BG9" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="BH9" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="BI9" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="BJ9" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="BK9" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="BL9" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="BM9" s="1" t="s">
         <v>921</v>
       </c>
-      <c r="BF9" s="1" t="s">
-        <v>922</v>
-      </c>
-      <c r="BG9" s="1" t="s">
-        <v>923</v>
-      </c>
-      <c r="BH9" s="1" t="s">
-        <v>924</v>
-      </c>
-      <c r="BI9" s="1" t="s">
-        <v>925</v>
-      </c>
-      <c r="BJ9" s="1" t="s">
-        <v>926</v>
-      </c>
-      <c r="BK9" s="1" t="s">
-        <v>927</v>
-      </c>
-      <c r="BL9" s="1" t="s">
-        <v>928</v>
-      </c>
-      <c r="BM9" s="1" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="10" spans="1:65" ht="28">
+      <c r="BO9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="BP9" s="1" t="s">
+        <v>1138</v>
+      </c>
+      <c r="BQ9" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="BR9" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="BS9" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="BT9" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="BU9" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="BV9" s="1" t="s">
+        <v>1144</v>
+      </c>
+      <c r="BW9" s="1" t="s">
+        <v>1145</v>
+      </c>
+      <c r="BX9" s="1" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="10" spans="1:87" ht="28">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
@@ -5833,8 +9979,38 @@
       <c r="U10" s="1" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="11" spans="1:65" ht="28">
+      <c r="BO10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BP10" s="1" t="s">
+        <v>1028</v>
+      </c>
+      <c r="BQ10" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="BR10" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="BS10" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="BT10" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="BU10" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="BV10" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="BW10" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="BX10" s="1" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="11" spans="1:87" ht="28">
       <c r="A11" s="2" t="s">
         <v>8</v>
       </c>
@@ -5895,8 +10071,38 @@
       <c r="U11" s="1" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="12" spans="1:65" ht="28">
+      <c r="BO11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="BP11" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="BQ11" s="1" t="s">
+        <v>1037</v>
+      </c>
+      <c r="BR11" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="BS11" s="1" t="s">
+        <v>1039</v>
+      </c>
+      <c r="BT11" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="BU11" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="BV11" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="BW11" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="BX11" s="1" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="12" spans="1:87" ht="28">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
@@ -5957,8 +10163,38 @@
       <c r="U12" s="1" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="13" spans="1:65" ht="28">
+      <c r="BO12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="BP12" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="BQ12" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="BR12" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="BS12" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="BT12" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="BU12" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="BV12" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="BW12" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="BX12" s="1" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="13" spans="1:87" ht="28">
       <c r="A13" s="2" t="s">
         <v>10</v>
       </c>
@@ -6019,8 +10255,38 @@
       <c r="U13" s="1" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="14" spans="1:65" ht="28">
+      <c r="BO13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="BP13" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="BQ13" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="BR13" s="1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="BS13" s="1" t="s">
+        <v>1150</v>
+      </c>
+      <c r="BT13" s="1" t="s">
+        <v>1151</v>
+      </c>
+      <c r="BU13" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="BV13" s="1" t="s">
+        <v>1056</v>
+      </c>
+      <c r="BW13" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="BX13" s="1" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="14" spans="1:87" ht="28">
       <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
@@ -6081,8 +10347,38 @@
       <c r="U14" s="1" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="15" spans="1:65" ht="28">
+      <c r="BO14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="BP14" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="BQ14" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="BR14" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="BS14" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="BT14" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="BU14" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="BV14" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="BW14" s="1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="BX14" s="1" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="15" spans="1:87" ht="28">
       <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
@@ -6143,8 +10439,38 @@
       <c r="U15" s="1" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="16" spans="1:65" ht="28">
+      <c r="BO15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="BP15" s="1" t="s">
+        <v>1068</v>
+      </c>
+      <c r="BQ15" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="BR15" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="BS15" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="BT15" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="BU15" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="BV15" s="1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="BW15" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="BX15" s="1" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="16" spans="1:87" ht="28">
       <c r="A16" s="2"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -6245,8 +10571,38 @@
       <c r="AQ16" s="1" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="17" spans="1:65" ht="28">
+      <c r="BZ16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="CA16" s="1" t="s">
+        <v>1300</v>
+      </c>
+      <c r="CB16" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="CC16" s="1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="CD16" s="1" t="s">
+        <v>1303</v>
+      </c>
+      <c r="CE16" s="1" t="s">
+        <v>1304</v>
+      </c>
+      <c r="CF16" s="1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="CG16" s="1" t="s">
+        <v>1306</v>
+      </c>
+      <c r="CH16" s="1" t="s">
+        <v>1307</v>
+      </c>
+      <c r="CI16" s="1" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="17" spans="1:87" ht="28">
       <c r="A17" s="2" t="s">
         <v>193</v>
       </c>
@@ -6281,64 +10637,64 @@
         <v>193</v>
       </c>
       <c r="AI17" s="1" t="s">
-        <v>746</v>
+        <v>1290</v>
       </c>
       <c r="AJ17" s="1" t="s">
-        <v>747</v>
+        <v>1291</v>
       </c>
       <c r="AK17" s="1" t="s">
-        <v>748</v>
+        <v>1292</v>
       </c>
       <c r="AL17" s="1" t="s">
-        <v>749</v>
+        <v>1293</v>
       </c>
       <c r="AM17" s="1" t="s">
-        <v>750</v>
+        <v>1294</v>
       </c>
       <c r="AN17" s="1" t="s">
-        <v>751</v>
+        <v>1295</v>
       </c>
       <c r="AO17" s="1" t="s">
-        <v>752</v>
+        <v>1296</v>
       </c>
       <c r="AP17" s="1" t="s">
-        <v>753</v>
+        <v>1297</v>
       </c>
       <c r="AQ17" s="1" t="s">
-        <v>754</v>
+        <v>1298</v>
       </c>
       <c r="BD17" s="2" t="s">
         <v>193</v>
       </c>
       <c r="BE17" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="BF17" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="BG17" s="1" t="s">
+        <v>924</v>
+      </c>
+      <c r="BH17" s="1" t="s">
+        <v>925</v>
+      </c>
+      <c r="BI17" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="BJ17" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="BK17" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="BL17" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="BM17" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="BF17" s="1" t="s">
-        <v>931</v>
-      </c>
-      <c r="BG17" s="1" t="s">
-        <v>932</v>
-      </c>
-      <c r="BH17" s="1" t="s">
-        <v>933</v>
-      </c>
-      <c r="BI17" s="1" t="s">
-        <v>934</v>
-      </c>
-      <c r="BJ17" s="1" t="s">
-        <v>935</v>
-      </c>
-      <c r="BK17" s="1" t="s">
-        <v>936</v>
-      </c>
-      <c r="BL17" s="1" t="s">
-        <v>937</v>
-      </c>
-      <c r="BM17" s="1" t="s">
-        <v>938</v>
-      </c>
-    </row>
-    <row r="18" spans="1:65" ht="42">
+    </row>
+    <row r="18" spans="1:87" ht="28">
       <c r="A18" s="2" t="s">
         <v>14</v>
       </c>
@@ -6463,34 +10819,94 @@
         <v>14</v>
       </c>
       <c r="BE18" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="BF18" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="BG18" s="1" t="s">
+        <v>933</v>
+      </c>
+      <c r="BH18" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="BI18" s="1" t="s">
+        <v>935</v>
+      </c>
+      <c r="BJ18" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="BK18" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="BL18" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="BM18" s="1" t="s">
         <v>939</v>
       </c>
-      <c r="BF18" s="1" t="s">
-        <v>940</v>
-      </c>
-      <c r="BG18" s="1" t="s">
-        <v>941</v>
-      </c>
-      <c r="BH18" s="1" t="s">
-        <v>942</v>
-      </c>
-      <c r="BI18" s="1" t="s">
-        <v>943</v>
-      </c>
-      <c r="BJ18" s="1" t="s">
-        <v>944</v>
-      </c>
-      <c r="BK18" s="1" t="s">
-        <v>945</v>
-      </c>
-      <c r="BL18" s="1" t="s">
-        <v>946</v>
-      </c>
-      <c r="BM18" s="1" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="19" spans="1:65">
+      <c r="BO18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="BP18" s="1" t="s">
+        <v>935</v>
+      </c>
+      <c r="BQ18" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="BR18" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="BS18" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="BT18" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="BU18" s="1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="BV18" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="BW18" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="BX18" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="BZ18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="CA18" s="1" t="s">
+        <v>1316</v>
+      </c>
+      <c r="CB18" s="1" t="s">
+        <v>1317</v>
+      </c>
+      <c r="CC18" s="1" t="s">
+        <v>1318</v>
+      </c>
+      <c r="CD18" s="1" t="s">
+        <v>1319</v>
+      </c>
+      <c r="CE18" s="1" t="s">
+        <v>1320</v>
+      </c>
+      <c r="CF18" s="1" t="s">
+        <v>1321</v>
+      </c>
+      <c r="CG18" s="1" t="s">
+        <v>1322</v>
+      </c>
+      <c r="CH18" s="1" t="s">
+        <v>1323</v>
+      </c>
+      <c r="CI18" s="1" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="19" spans="1:87">
       <c r="A19" s="2" t="s">
         <v>15</v>
       </c>
@@ -6621,34 +11037,94 @@
         <v>15</v>
       </c>
       <c r="BE19" s="1" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="BF19" s="1" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
       <c r="BG19" s="1" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="BH19" s="1" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="BI19" s="1" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="BJ19" s="1" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="BK19" s="1" t="s">
         <v>269</v>
       </c>
       <c r="BL19" s="1" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="BM19" s="1" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="20" spans="1:65" ht="42">
+        <v>942</v>
+      </c>
+      <c r="BO19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="BP19" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="BQ19" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BR19" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="BS19" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="BT19" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BU19" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="BV19" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="BW19" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="BX19" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="BZ19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="CA19" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="CB19" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="CC19" s="1" t="s">
+        <v>1310</v>
+      </c>
+      <c r="CD19" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="CE19" s="1" t="s">
+        <v>1312</v>
+      </c>
+      <c r="CF19" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="CG19" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="CH19" s="1" t="s">
+        <v>1314</v>
+      </c>
+      <c r="CI19" s="1" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="20" spans="1:87" ht="42">
       <c r="A20" s="2" t="s">
         <v>16</v>
       </c>
@@ -6743,64 +11219,124 @@
         <v>16</v>
       </c>
       <c r="AI20" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="AJ20" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="AK20" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="AL20" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="AM20" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="AN20" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="AO20" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="AP20" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="AQ20" s="1" t="s">
         <v>755</v>
-      </c>
-      <c r="AJ20" s="1" t="s">
-        <v>756</v>
-      </c>
-      <c r="AK20" s="1" t="s">
-        <v>757</v>
-      </c>
-      <c r="AL20" s="1" t="s">
-        <v>758</v>
-      </c>
-      <c r="AM20" s="1" t="s">
-        <v>759</v>
-      </c>
-      <c r="AN20" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="AO20" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="AP20" s="1" t="s">
-        <v>762</v>
-      </c>
-      <c r="AQ20" s="1" t="s">
-        <v>763</v>
       </c>
       <c r="BD20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="BE20" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="BF20" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="BG20" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="BH20" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="BI20" s="1" t="s">
+        <v>948</v>
+      </c>
+      <c r="BJ20" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="BK20" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="BL20" s="1" t="s">
+        <v>951</v>
+      </c>
+      <c r="BM20" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="BF20" s="1" t="s">
-        <v>953</v>
-      </c>
-      <c r="BG20" s="1" t="s">
-        <v>954</v>
-      </c>
-      <c r="BH20" s="1" t="s">
-        <v>955</v>
-      </c>
-      <c r="BI20" s="1" t="s">
-        <v>956</v>
-      </c>
-      <c r="BJ20" s="1" t="s">
-        <v>957</v>
-      </c>
-      <c r="BK20" s="1" t="s">
-        <v>958</v>
-      </c>
-      <c r="BL20" s="1" t="s">
-        <v>959</v>
-      </c>
-      <c r="BM20" s="1" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="21" spans="1:65" ht="42">
+      <c r="BO20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="BP20" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="BQ20" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="BR20" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="BS20" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="BT20" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="BU20" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="BV20" s="1" t="s">
+        <v>1091</v>
+      </c>
+      <c r="BW20" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="BX20" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="BZ20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="CA20" s="1" t="s">
+        <v>1325</v>
+      </c>
+      <c r="CB20" s="1" t="s">
+        <v>1326</v>
+      </c>
+      <c r="CC20" s="1" t="s">
+        <v>1327</v>
+      </c>
+      <c r="CD20" s="1" t="s">
+        <v>1328</v>
+      </c>
+      <c r="CE20" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="CF20" s="1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="CG20" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="CH20" s="1" t="s">
+        <v>1332</v>
+      </c>
+      <c r="CI20" s="1" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="21" spans="1:87" ht="42">
       <c r="A21" s="2" t="s">
         <v>17</v>
       </c>
@@ -6895,64 +11431,124 @@
         <v>17</v>
       </c>
       <c r="AI21" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="AJ21" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="AK21" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="AL21" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="AM21" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="AN21" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="AO21" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="AP21" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="AQ21" s="1" t="s">
         <v>764</v>
-      </c>
-      <c r="AJ21" s="1" t="s">
-        <v>765</v>
-      </c>
-      <c r="AK21" s="1" t="s">
-        <v>766</v>
-      </c>
-      <c r="AL21" s="1" t="s">
-        <v>767</v>
-      </c>
-      <c r="AM21" s="1" t="s">
-        <v>768</v>
-      </c>
-      <c r="AN21" s="1" t="s">
-        <v>769</v>
-      </c>
-      <c r="AO21" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="AP21" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="AQ21" s="1" t="s">
-        <v>772</v>
       </c>
       <c r="BD21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="BE21" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="BF21" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="BG21" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="BH21" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="BI21" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="BJ21" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="BK21" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="BL21" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="BM21" s="1" t="s">
         <v>961</v>
       </c>
-      <c r="BF21" s="1" t="s">
-        <v>962</v>
-      </c>
-      <c r="BG21" s="1" t="s">
-        <v>963</v>
-      </c>
-      <c r="BH21" s="1" t="s">
-        <v>964</v>
-      </c>
-      <c r="BI21" s="1" t="s">
-        <v>965</v>
-      </c>
-      <c r="BJ21" s="1" t="s">
-        <v>966</v>
-      </c>
-      <c r="BK21" s="1" t="s">
-        <v>967</v>
-      </c>
-      <c r="BL21" s="1" t="s">
-        <v>968</v>
-      </c>
-      <c r="BM21" s="1" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="22" spans="1:65" ht="28">
+      <c r="BO21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BP21" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="BQ21" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="BR21" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="BS21" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="BT21" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="BU21" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="BV21" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="BW21" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="BX21" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="BZ21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="CA21" s="1" t="s">
+        <v>1334</v>
+      </c>
+      <c r="CB21" s="1" t="s">
+        <v>1335</v>
+      </c>
+      <c r="CC21" s="1" t="s">
+        <v>1336</v>
+      </c>
+      <c r="CD21" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="CE21" s="1" t="s">
+        <v>1338</v>
+      </c>
+      <c r="CF21" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="CG21" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="CH21" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="CI21" s="1" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="22" spans="1:87" ht="28">
       <c r="A22" s="2" t="s">
         <v>18</v>
       </c>
@@ -7047,64 +11643,124 @@
         <v>18</v>
       </c>
       <c r="AI22" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="AJ22" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="AK22" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="AL22" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="AM22" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="AN22" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="AO22" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="AP22" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="AQ22" s="1" t="s">
         <v>773</v>
-      </c>
-      <c r="AJ22" s="1" t="s">
-        <v>774</v>
-      </c>
-      <c r="AK22" s="1" t="s">
-        <v>775</v>
-      </c>
-      <c r="AL22" s="1" t="s">
-        <v>776</v>
-      </c>
-      <c r="AM22" s="1" t="s">
-        <v>777</v>
-      </c>
-      <c r="AN22" s="1" t="s">
-        <v>778</v>
-      </c>
-      <c r="AO22" s="1" t="s">
-        <v>779</v>
-      </c>
-      <c r="AP22" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="AQ22" s="1" t="s">
-        <v>781</v>
       </c>
       <c r="BD22" s="2" t="s">
         <v>18</v>
       </c>
       <c r="BE22" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="BF22" s="1" t="s">
+        <v>963</v>
+      </c>
+      <c r="BG22" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="BH22" s="1" t="s">
+        <v>965</v>
+      </c>
+      <c r="BI22" s="1" t="s">
+        <v>966</v>
+      </c>
+      <c r="BJ22" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="BK22" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="BL22" s="1" t="s">
+        <v>969</v>
+      </c>
+      <c r="BM22" s="1" t="s">
         <v>970</v>
       </c>
-      <c r="BF22" s="1" t="s">
-        <v>971</v>
-      </c>
-      <c r="BG22" s="1" t="s">
-        <v>972</v>
-      </c>
-      <c r="BH22" s="1" t="s">
-        <v>973</v>
-      </c>
-      <c r="BI22" s="1" t="s">
-        <v>974</v>
-      </c>
-      <c r="BJ22" s="1" t="s">
-        <v>975</v>
-      </c>
-      <c r="BK22" s="1" t="s">
-        <v>976</v>
-      </c>
-      <c r="BL22" s="1" t="s">
-        <v>977</v>
-      </c>
-      <c r="BM22" s="1" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="23" spans="1:65">
+      <c r="BO22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="BP22" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="BQ22" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="BR22" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="BS22" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="BT22" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="BU22" s="1" t="s">
+        <v>1108</v>
+      </c>
+      <c r="BV22" s="1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="BW22" s="1" t="s">
+        <v>1110</v>
+      </c>
+      <c r="BX22" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="BZ22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="CA22" s="1" t="s">
+        <v>1343</v>
+      </c>
+      <c r="CB22" s="1" t="s">
+        <v>1344</v>
+      </c>
+      <c r="CC22" s="1" t="s">
+        <v>1345</v>
+      </c>
+      <c r="CD22" s="1" t="s">
+        <v>1346</v>
+      </c>
+      <c r="CE22" s="1" t="s">
+        <v>1347</v>
+      </c>
+      <c r="CF22" s="1" t="s">
+        <v>1348</v>
+      </c>
+      <c r="CG22" s="1" t="s">
+        <v>1349</v>
+      </c>
+      <c r="CH22" s="1" t="s">
+        <v>1350</v>
+      </c>
+      <c r="CI22" s="1" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="23" spans="1:87">
       <c r="A23" s="2" t="s">
         <v>19</v>
       </c>
@@ -7199,28 +11855,28 @@
         <v>19</v>
       </c>
       <c r="AI23" s="1" t="s">
-        <v>782</v>
+        <v>774</v>
       </c>
       <c r="AJ23" s="1" t="s">
-        <v>783</v>
+        <v>775</v>
       </c>
       <c r="AK23" s="1" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="AL23" s="1" t="s">
-        <v>785</v>
+        <v>777</v>
       </c>
       <c r="AM23" s="1" t="s">
-        <v>786</v>
+        <v>778</v>
       </c>
       <c r="AN23" s="1" t="s">
-        <v>787</v>
+        <v>779</v>
       </c>
       <c r="AO23" s="1" t="s">
-        <v>788</v>
+        <v>780</v>
       </c>
       <c r="AP23" s="1" t="s">
-        <v>789</v>
+        <v>781</v>
       </c>
       <c r="AQ23" s="1" t="s">
         <v>470</v>
@@ -7229,34 +11885,46 @@
         <v>19</v>
       </c>
       <c r="BE23" s="1" t="s">
+        <v>971</v>
+      </c>
+      <c r="BF23" s="1" t="s">
+        <v>972</v>
+      </c>
+      <c r="BG23" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="BH23" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="BI23" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="BJ23" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="BK23" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="BL23" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="BM23" s="1" t="s">
         <v>979</v>
       </c>
-      <c r="BF23" s="1" t="s">
-        <v>980</v>
-      </c>
-      <c r="BG23" s="1" t="s">
-        <v>981</v>
-      </c>
-      <c r="BH23" s="1" t="s">
-        <v>982</v>
-      </c>
-      <c r="BI23" s="1" t="s">
-        <v>983</v>
-      </c>
-      <c r="BJ23" s="1" t="s">
-        <v>984</v>
-      </c>
-      <c r="BK23" s="1" t="s">
-        <v>985</v>
-      </c>
-      <c r="BL23" s="1" t="s">
-        <v>986</v>
-      </c>
-      <c r="BM23" s="1" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="24" spans="1:65">
+      <c r="BO23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="BP23" s="1"/>
+      <c r="BQ23" s="1"/>
+      <c r="BR23" s="1"/>
+      <c r="BS23" s="1"/>
+      <c r="BT23" s="1"/>
+      <c r="BU23" s="1"/>
+      <c r="BV23" s="1"/>
+      <c r="BW23" s="1"/>
+      <c r="BX23" s="1"/>
+    </row>
+    <row r="24" spans="1:87">
       <c r="A24" s="2" t="s">
         <v>20</v>
       </c>
@@ -7351,34 +12019,34 @@
         <v>20</v>
       </c>
       <c r="AI24" s="1" t="s">
-        <v>790</v>
+        <v>782</v>
       </c>
       <c r="AJ24" s="1" t="s">
-        <v>791</v>
+        <v>783</v>
       </c>
       <c r="AK24" s="1" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="AL24" s="1" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="AM24" s="1" t="s">
-        <v>794</v>
+        <v>786</v>
       </c>
       <c r="AN24" s="1" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="AO24" s="1" t="s">
-        <v>796</v>
+        <v>788</v>
       </c>
       <c r="AP24" s="1" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="AQ24" s="1" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="25" spans="1:65">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="25" spans="1:87">
       <c r="L25" s="2" t="s">
         <v>21</v>
       </c>
@@ -7413,34 +12081,34 @@
         <v>21</v>
       </c>
       <c r="AI25" s="1" t="s">
-        <v>797</v>
+        <v>789</v>
       </c>
       <c r="AJ25" s="1" t="s">
         <v>263</v>
       </c>
       <c r="AK25" s="1" t="s">
-        <v>798</v>
+        <v>790</v>
       </c>
       <c r="AL25" s="1" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="AM25" s="1" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="AN25" s="1" t="s">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="AO25" s="1" t="s">
-        <v>802</v>
+        <v>794</v>
       </c>
       <c r="AP25" s="1" t="s">
-        <v>803</v>
+        <v>795</v>
       </c>
       <c r="AQ25" s="1" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="26" spans="1:65">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="26" spans="1:87">
       <c r="L26" s="2" t="s">
         <v>22</v>
       </c>
@@ -7475,34 +12143,34 @@
         <v>22</v>
       </c>
       <c r="AI26" s="1" t="s">
-        <v>805</v>
+        <v>797</v>
       </c>
       <c r="AJ26" s="1" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="AK26" s="1" t="s">
         <v>251</v>
       </c>
       <c r="AL26" s="1" t="s">
-        <v>791</v>
+        <v>783</v>
       </c>
       <c r="AM26" s="1" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="AN26" s="1" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="AO26" s="1" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="AP26" s="1" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="AQ26" s="1" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="27" spans="1:65">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="27" spans="1:87">
       <c r="A27" s="2" t="s">
         <v>23</v>
       </c>
@@ -7567,34 +12235,34 @@
         <v>23</v>
       </c>
       <c r="AI27" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="AJ27" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="AK27" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="AL27" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="AM27" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="AN27" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="AO27" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="AP27" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="AQ27" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="AJ27" s="1" t="s">
-        <v>807</v>
-      </c>
-      <c r="AK27" s="1" t="s">
-        <v>808</v>
-      </c>
-      <c r="AL27" s="1" t="s">
-        <v>809</v>
-      </c>
-      <c r="AM27" s="1" t="s">
-        <v>810</v>
-      </c>
-      <c r="AN27" s="1" t="s">
-        <v>811</v>
-      </c>
-      <c r="AO27" s="1" t="s">
-        <v>812</v>
-      </c>
-      <c r="AP27" s="1" t="s">
-        <v>813</v>
-      </c>
-      <c r="AQ27" s="1" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="28" spans="1:65">
+    </row>
+    <row r="28" spans="1:87">
       <c r="A28" s="2" t="s">
         <v>24</v>
       </c>
@@ -7659,34 +12327,34 @@
         <v>24</v>
       </c>
       <c r="AI28" s="1" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="AJ28" s="1" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="AK28" s="1" t="s">
-        <v>817</v>
+        <v>809</v>
       </c>
       <c r="AL28" s="1" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="AM28" s="1" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="AN28" s="1" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="AO28" s="1" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="AP28" s="1" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="AQ28" s="1" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="29" spans="1:65" ht="42">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="29" spans="1:87" ht="42">
       <c r="A29" s="2" t="s">
         <v>25</v>
       </c>
@@ -7837,8 +12505,38 @@
       <c r="BM29" s="1" t="s">
         <v>616</v>
       </c>
-    </row>
-    <row r="30" spans="1:65">
+      <c r="BO29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="BP29" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="BQ29" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="BR29" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="BS29" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="BT29" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="BU29" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="BV29" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="BW29" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="BX29" s="1" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="30" spans="1:87">
       <c r="AS30" s="1"/>
       <c r="AT30" s="2" t="s">
         <v>81</v>
@@ -7868,135 +12566,135 @@
         <v>88</v>
       </c>
     </row>
-    <row r="31" spans="1:65" ht="28">
+    <row r="31" spans="1:87" ht="28">
       <c r="AS31" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="AT31" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="AU31" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="AV31" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="AW31" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="AX31" s="1" t="s">
+        <v>825</v>
+      </c>
+      <c r="AY31" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="AZ31" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="BA31" s="1" t="s">
         <v>828</v>
       </c>
-      <c r="AT31" s="1" t="s">
+      <c r="BB31" s="1" t="s">
         <v>829</v>
       </c>
-      <c r="AU31" s="1" t="s">
+    </row>
+    <row r="32" spans="1:87" ht="28">
+      <c r="AS32" s="2" t="s">
         <v>830</v>
       </c>
-      <c r="AV31" s="1" t="s">
+      <c r="AT32" s="1" t="s">
         <v>831</v>
       </c>
-      <c r="AW31" s="1" t="s">
+      <c r="AU32" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="AX31" s="1" t="s">
+      <c r="AV32" s="1" t="s">
         <v>833</v>
       </c>
-      <c r="AY31" s="1" t="s">
+      <c r="AW32" s="1" t="s">
         <v>834</v>
       </c>
-      <c r="AZ31" s="1" t="s">
+      <c r="AX32" s="1" t="s">
         <v>835</v>
       </c>
-      <c r="BA31" s="1" t="s">
+      <c r="AY32" s="1" t="s">
         <v>836</v>
       </c>
-      <c r="BB31" s="1" t="s">
+      <c r="AZ32" s="1" t="s">
         <v>837</v>
       </c>
-    </row>
-    <row r="32" spans="1:65" ht="28">
-      <c r="AS32" s="2" t="s">
+      <c r="BA32" s="1" t="s">
         <v>838</v>
       </c>
-      <c r="AT32" s="1" t="s">
+      <c r="BB32" s="1" t="s">
         <v>839</v>
       </c>
-      <c r="AU32" s="1" t="s">
+    </row>
+    <row r="33" spans="24:76" ht="28">
+      <c r="AS33" s="2" t="s">
         <v>840</v>
       </c>
-      <c r="AV32" s="1" t="s">
+      <c r="AT33" s="1" t="s">
         <v>841</v>
       </c>
-      <c r="AW32" s="1" t="s">
+      <c r="AU33" s="1" t="s">
         <v>842</v>
       </c>
-      <c r="AX32" s="1" t="s">
+      <c r="AV33" s="1" t="s">
         <v>843</v>
       </c>
-      <c r="AY32" s="1" t="s">
+      <c r="AW33" s="1" t="s">
         <v>844</v>
       </c>
-      <c r="AZ32" s="1" t="s">
+      <c r="AX33" s="1" t="s">
         <v>845</v>
       </c>
-      <c r="BA32" s="1" t="s">
+      <c r="AY33" s="1" t="s">
         <v>846</v>
       </c>
-      <c r="BB32" s="1" t="s">
+      <c r="AZ33" s="1" t="s">
         <v>847</v>
       </c>
-    </row>
-    <row r="33" spans="24:65" ht="28">
-      <c r="AS33" s="2" t="s">
+      <c r="BA33" s="1" t="s">
         <v>848</v>
       </c>
-      <c r="AT33" s="1" t="s">
+      <c r="BB33" s="1" t="s">
         <v>849</v>
       </c>
-      <c r="AU33" s="1" t="s">
+    </row>
+    <row r="34" spans="24:76" ht="28">
+      <c r="AS34" s="2" t="s">
         <v>850</v>
       </c>
-      <c r="AV33" s="1" t="s">
+      <c r="AT34" s="1" t="s">
         <v>851</v>
       </c>
-      <c r="AW33" s="1" t="s">
+      <c r="AU34" s="1" t="s">
         <v>852</v>
       </c>
-      <c r="AX33" s="1" t="s">
+      <c r="AV34" s="1" t="s">
         <v>853</v>
       </c>
-      <c r="AY33" s="1" t="s">
+      <c r="AW34" s="1" t="s">
         <v>854</v>
       </c>
-      <c r="AZ33" s="1" t="s">
+      <c r="AX34" s="1" t="s">
         <v>855</v>
       </c>
-      <c r="BA33" s="1" t="s">
+      <c r="AY34" s="1" t="s">
         <v>856</v>
       </c>
-      <c r="BB33" s="1" t="s">
+      <c r="AZ34" s="1" t="s">
         <v>857</v>
       </c>
-    </row>
-    <row r="34" spans="24:65" ht="28">
-      <c r="AS34" s="2" t="s">
+      <c r="BA34" s="1" t="s">
         <v>858</v>
       </c>
-      <c r="AT34" s="1" t="s">
+      <c r="BB34" s="1" t="s">
         <v>859</v>
       </c>
-      <c r="AU34" s="1" t="s">
-        <v>860</v>
-      </c>
-      <c r="AV34" s="1" t="s">
-        <v>861</v>
-      </c>
-      <c r="AW34" s="1" t="s">
-        <v>862</v>
-      </c>
-      <c r="AX34" s="1" t="s">
-        <v>863</v>
-      </c>
-      <c r="AY34" s="1" t="s">
-        <v>864</v>
-      </c>
-      <c r="AZ34" s="1" t="s">
-        <v>865</v>
-      </c>
-      <c r="BA34" s="1" t="s">
-        <v>866</v>
-      </c>
-      <c r="BB34" s="1" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="35" spans="24:65" ht="42">
+    </row>
+    <row r="35" spans="24:76" ht="42">
       <c r="X35" s="2" t="s">
         <v>598</v>
       </c>
@@ -8028,34 +12726,64 @@
         <v>607</v>
       </c>
       <c r="BD35" s="2" t="s">
-        <v>997</v>
+        <v>989</v>
       </c>
       <c r="BE35" s="1" t="s">
-        <v>988</v>
+        <v>980</v>
       </c>
       <c r="BF35" s="1" t="s">
-        <v>989</v>
+        <v>981</v>
       </c>
       <c r="BG35" s="1" t="s">
-        <v>990</v>
+        <v>982</v>
       </c>
       <c r="BH35" s="1" t="s">
-        <v>991</v>
+        <v>983</v>
       </c>
       <c r="BI35" s="1" t="s">
-        <v>992</v>
+        <v>984</v>
       </c>
       <c r="BJ35" s="1" t="s">
-        <v>993</v>
+        <v>985</v>
       </c>
       <c r="BK35" s="1" t="s">
-        <v>994</v>
+        <v>986</v>
       </c>
       <c r="BL35" s="1" t="s">
-        <v>995</v>
+        <v>987</v>
       </c>
       <c r="BM35" s="1" t="s">
         <v>73</v>
+      </c>
+      <c r="BO35" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="BP35" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="BQ35" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="BR35" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="BS35" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="BT35" s="1" t="s">
+        <v>1116</v>
+      </c>
+      <c r="BU35" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="BV35" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="BW35" s="1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="BX35" s="1" t="s">
+        <v>1120</v>
       </c>
     </row>
   </sheetData>
@@ -8064,687 +12792,1732 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02CBA023-F667-4873-AB81-7046F0D2B181}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:S70"/>
   <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="14.5" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="8.6640625" style="14"/>
+    <col min="8" max="8" width="8.6640625" style="7"/>
+    <col min="11" max="11" width="10.25" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="19" width="8.58203125" style="1" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickTop="1" thickBot="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:8" ht="15" thickTop="1" thickBot="1">
+      <c r="A1" s="4" t="s">
         <v>710</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>617</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>711</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>712</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>708</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="6" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>713</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>714</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>715</v>
       </c>
-      <c r="E2" s="6">
-        <v>-1.7929999999999999</v>
-      </c>
-      <c r="F2" s="6">
-        <v>0.59199999999999997</v>
-      </c>
-      <c r="G2" s="6" t="s">
+      <c r="E2" s="7" t="s">
+        <v>1160</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>1162</v>
+      </c>
+      <c r="G2" s="7" t="s">
         <v>716</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="9"/>
-      <c r="B3" s="6">
-        <v>-2.6779999999999999</v>
-      </c>
-      <c r="C3" s="6">
-        <v>-3.6890000000000001</v>
-      </c>
-      <c r="D3" s="6">
-        <v>-1.494</v>
-      </c>
-      <c r="E3" s="6">
-        <v>-1.593</v>
-      </c>
-      <c r="F3" s="6">
-        <v>-1.665</v>
-      </c>
-      <c r="G3" s="6">
-        <v>-1.5669999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="9" t="s">
+      <c r="H2" s="7" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="15"/>
+      <c r="B3" s="7" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>1159</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>1161</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>1163</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>1164</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="6">
-        <v>0.621</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0.42299999999999999</v>
-      </c>
-      <c r="D4" s="6">
-        <v>0.11600000000000001</v>
-      </c>
-      <c r="E4" s="6">
-        <v>-0.27400000000000002</v>
-      </c>
-      <c r="F4" s="6">
-        <v>0.153</v>
-      </c>
-      <c r="G4" s="6">
-        <v>0.21199999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="9"/>
-      <c r="B5" s="6">
-        <v>-0.98099999999999998</v>
-      </c>
-      <c r="C5" s="6">
-        <v>-0.91400000000000003</v>
-      </c>
-      <c r="D5" s="6">
-        <v>-0.58899999999999997</v>
-      </c>
-      <c r="E5" s="6">
-        <v>-0.64200000000000002</v>
-      </c>
-      <c r="F5" s="6">
-        <v>-0.77400000000000002</v>
-      </c>
-      <c r="G5" s="6">
-        <v>-0.625</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="9" t="s">
+      <c r="B4" s="7" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>1171</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>1173</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>1175</v>
+      </c>
+      <c r="H4" s="7">
+        <v>0.70099999999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="11"/>
+      <c r="B5" s="7" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>1172</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>1174</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>1176</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="6">
-        <v>-0.02</v>
-      </c>
-      <c r="C6" s="6">
-        <v>2.4E-2</v>
-      </c>
-      <c r="D6" s="6">
-        <v>8.5999999999999993E-2</v>
-      </c>
-      <c r="E6" s="6">
-        <v>0.14199999999999999</v>
-      </c>
-      <c r="F6" s="6">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="G6" s="6">
-        <v>6.5000000000000002E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="9"/>
-      <c r="B7" s="6">
-        <v>-0.14099999999999999</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-0.13500000000000001</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-0.112</v>
-      </c>
-      <c r="E7" s="6">
-        <v>-0.122</v>
-      </c>
-      <c r="F7" s="6">
-        <v>-0.129</v>
-      </c>
-      <c r="G7" s="6">
-        <v>-0.115</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="9" t="s">
+      <c r="B6" s="7" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>1181</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>1187</v>
+      </c>
+      <c r="H6" s="7">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="11"/>
+      <c r="B7" s="7" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>1184</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>1186</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>1188</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="6">
-        <v>-6.0000000000000001E-3</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-0.02</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-3.2000000000000001E-2</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-3.5000000000000003E-2</v>
-      </c>
-      <c r="F8" s="6">
-        <v>-3.0000000000000001E-3</v>
-      </c>
-      <c r="G8" s="6">
-        <v>-2.5000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="9"/>
-      <c r="B9" s="6">
-        <v>-0.13900000000000001</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-0.13300000000000001</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-0.115</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-0.125</v>
-      </c>
-      <c r="F9" s="6">
-        <v>-0.13400000000000001</v>
-      </c>
-      <c r="G9" s="6">
-        <v>-0.11700000000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="9" t="s">
+      <c r="B8" s="7" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>1193</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>1195</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H8" s="7">
+        <v>-8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="11"/>
+      <c r="B9" s="7" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>1188</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>1194</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>1196</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>1198</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="6">
-        <v>4.7E-2</v>
-      </c>
-      <c r="C10" s="6">
-        <v>0.113</v>
-      </c>
-      <c r="D10" s="6">
-        <v>0.217</v>
-      </c>
-      <c r="E10" s="6">
-        <v>0.17</v>
-      </c>
-      <c r="F10" s="6">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="G10" s="6">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="9"/>
-      <c r="B11" s="6">
-        <v>-0.184</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-0.182</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-0.156</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-0.16900000000000001</v>
-      </c>
-      <c r="F11" s="6">
-        <v>-0.16500000000000001</v>
-      </c>
-      <c r="G11" s="6">
-        <v>-0.157</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="9" t="s">
+      <c r="B10" s="7" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>1206</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>1208</v>
+      </c>
+      <c r="H10" s="7">
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="11"/>
+      <c r="B11" s="7" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>1204</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>1205</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>1207</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>1209</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>717</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="7" t="s">
         <v>717</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="7" t="s">
         <v>718</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="7" t="s">
         <v>719</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="7" t="s">
         <v>720</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="7" t="s">
         <v>721</v>
       </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="9"/>
-      <c r="B13" s="6">
-        <v>-0.159</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-0.151</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-0.122</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-0.13100000000000001</v>
-      </c>
-      <c r="F13" s="6">
-        <v>-0.14399999999999999</v>
-      </c>
-      <c r="G13" s="6">
-        <v>-0.129</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="9" t="s">
+      <c r="H12" s="7" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="11"/>
+      <c r="B13" s="7" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>1212</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>1213</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>1186</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>722</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="7" t="s">
         <v>723</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="7" t="s">
         <v>724</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="7" t="s">
         <v>725</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="7" t="s">
         <v>726</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="7" t="s">
         <v>727</v>
       </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="9"/>
-      <c r="B15" s="6">
-        <v>-0.76700000000000002</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-0.74399999999999999</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-0.55900000000000005</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-0.57299999999999995</v>
-      </c>
-      <c r="F15" s="6">
-        <v>-0.63900000000000001</v>
-      </c>
-      <c r="G15" s="6">
-        <v>-0.65100000000000002</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="9" t="s">
+      <c r="H14" s="7" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="11"/>
+      <c r="B15" s="7" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>1216</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>1217</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>1218</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>1219</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="6">
-        <v>-1.044</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-0.55600000000000005</v>
-      </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="9"/>
-      <c r="B17" s="6">
-        <v>-1.3320000000000001</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-1.4670000000000001</v>
-      </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="9" t="s">
+      <c r="B16" s="7" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="7">
+        <v>-1.6479999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="11"/>
+      <c r="B17" s="7" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="7" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="6">
-        <v>0.34499999999999997</v>
-      </c>
-      <c r="C18" s="6" t="s">
+      <c r="B18" s="7" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>728</v>
       </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="9"/>
-      <c r="B19" s="6">
-        <v>-0.23100000000000001</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-0.27200000000000002</v>
-      </c>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="9" t="s">
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="7" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="11"/>
+      <c r="B19" s="7" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="7" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="6">
-        <v>-0.23499999999999999</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-0.27</v>
-      </c>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="9"/>
-      <c r="B21" s="6">
-        <v>-0.23300000000000001</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-0.27300000000000002</v>
-      </c>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="9" t="s">
+      <c r="B20" s="7" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="7">
+        <v>-0.34300000000000003</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="11"/>
+      <c r="B21" s="7" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="7" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="6">
-        <v>0.499</v>
-      </c>
-      <c r="C22" s="6">
-        <v>0.57699999999999996</v>
-      </c>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="9"/>
-      <c r="B23" s="6">
-        <v>-0.32400000000000001</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-0.38100000000000001</v>
-      </c>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="9" t="s">
+      <c r="B22" s="7" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="7" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="11"/>
+      <c r="B23" s="7" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>1234</v>
+      </c>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="7" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B24" s="6">
-        <v>-8.8999999999999996E-2</v>
-      </c>
-      <c r="C24" s="6">
-        <v>0.19500000000000001</v>
-      </c>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="9"/>
-      <c r="B25" s="6">
-        <v>-0.26500000000000001</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-0.30299999999999999</v>
-      </c>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="9" t="s">
+      <c r="B24" s="7" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="7">
+        <v>0.13900000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="11"/>
+      <c r="B25" s="7" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>1238</v>
+      </c>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="7" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B26" s="6">
-        <v>1.466</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-6.5000000000000002E-2</v>
-      </c>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="9"/>
-      <c r="B27" s="6">
-        <v>-1.113</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-1.2729999999999999</v>
-      </c>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="9" t="s">
+      <c r="B26" s="7" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="7">
+        <v>0.44400000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="11"/>
+      <c r="B27" s="7" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="7" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="11" t="s">
         <v>729</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="7" t="s">
         <v>730</v>
       </c>
-      <c r="C28" s="12"/>
-      <c r="D28" s="6" t="s">
+      <c r="C28" s="13"/>
+      <c r="D28" s="7" t="s">
         <v>721</v>
       </c>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="6" t="s">
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="7" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="9"/>
-      <c r="B29" s="6">
-        <v>-9.0999999999999998E-2</v>
-      </c>
-      <c r="C29" s="12"/>
-      <c r="D29" s="6">
-        <v>-7.9000000000000001E-2</v>
-      </c>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="6">
-        <v>-0.17799999999999999</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="9" t="s">
+    <row r="29" spans="1:8">
+      <c r="A29" s="11"/>
+      <c r="B29" s="7" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C29" s="13"/>
+      <c r="D29" s="7" t="s">
+        <v>1244</v>
+      </c>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="7" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="11" t="s">
         <v>729</v>
       </c>
-      <c r="B30" s="12"/>
-      <c r="C30" s="6" t="s">
+      <c r="B30" s="13"/>
+      <c r="C30" s="7" t="s">
         <v>718</v>
       </c>
-      <c r="D30" s="12"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="6" t="s">
+      <c r="D30" s="13"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="7" t="s">
         <v>732</v>
       </c>
-      <c r="G30" s="12"/>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="9"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="6">
-        <v>-0.09</v>
-      </c>
-      <c r="D31" s="12"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="6">
-        <v>-8.5999999999999993E-2</v>
-      </c>
-      <c r="G31" s="12"/>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="9" t="s">
+      <c r="G30" s="13"/>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="11"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="7" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D31" s="13"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="7" t="s">
+        <v>1247</v>
+      </c>
+      <c r="G31" s="13"/>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B32" s="6">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="C32" s="6">
-        <v>0.17299999999999999</v>
-      </c>
-      <c r="D32" s="6">
-        <v>4.3999999999999997E-2</v>
-      </c>
-      <c r="E32" s="11"/>
-      <c r="F32" s="6">
-        <v>0.19900000000000001</v>
-      </c>
-      <c r="G32" s="6">
-        <v>2.9000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="9"/>
-      <c r="B33" s="6" t="s">
+      <c r="B32" s="7" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E32" s="12"/>
+      <c r="F32" s="7" t="s">
+        <v>1251</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>1252</v>
+      </c>
+      <c r="H32" s="7">
+        <v>0.159</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
+      <c r="A33" s="11"/>
+      <c r="B33" s="7" t="s">
         <v>733</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="7" t="s">
         <v>734</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D33" s="7" t="s">
         <v>735</v>
       </c>
-      <c r="E33" s="11"/>
-      <c r="F33" s="6" t="s">
+      <c r="E33" s="12"/>
+      <c r="F33" s="7" t="s">
         <v>734</v>
       </c>
-      <c r="G33" s="6" t="s">
+      <c r="G33" s="7" t="s">
         <v>736</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" ht="14.5" thickBot="1">
-      <c r="A34" s="7" t="s">
+      <c r="H33" s="7" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" ht="14.5" thickBot="1">
+      <c r="A34" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B34" s="8">
-        <v>0.65600000000000003</v>
-      </c>
-      <c r="C34" s="8">
-        <v>0.61499999999999999</v>
-      </c>
-      <c r="D34" s="8">
-        <v>0.64300000000000002</v>
-      </c>
-      <c r="E34" s="8">
-        <v>0.59</v>
-      </c>
-      <c r="F34" s="8">
-        <v>0.58299999999999996</v>
-      </c>
-      <c r="G34" s="8">
-        <v>0.64700000000000002</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="14.5" thickTop="1"/>
+      <c r="B34" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>706</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>940</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>700</v>
+      </c>
+      <c r="H34" s="9">
+        <v>0.61699999999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="15" thickTop="1" thickBot="1"/>
+    <row r="36" spans="1:19" ht="14.5" thickTop="1">
+      <c r="K36" s="45" t="s">
+        <v>1353</v>
+      </c>
+      <c r="L36" s="46" t="s">
+        <v>1352</v>
+      </c>
+      <c r="M36" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="N36" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="O36" s="46" t="s">
+        <v>618</v>
+      </c>
+      <c r="P36" s="46" t="s">
+        <v>1277</v>
+      </c>
+      <c r="Q36" s="46" t="s">
+        <v>988</v>
+      </c>
+      <c r="R36" s="46" t="s">
+        <v>709</v>
+      </c>
+      <c r="S36" s="46" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" ht="27">
+      <c r="K37" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="L37" s="39"/>
+      <c r="M37" s="39" t="s">
+        <v>278</v>
+      </c>
+      <c r="N37" s="39" t="s">
+        <v>89</v>
+      </c>
+      <c r="O37" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="P37" s="39" t="s">
+        <v>813</v>
+      </c>
+      <c r="Q37" s="39" t="s">
+        <v>860</v>
+      </c>
+      <c r="R37" s="39" t="s">
+        <v>619</v>
+      </c>
+      <c r="S37" s="39" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" ht="27">
+      <c r="K38" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="L38" s="39"/>
+      <c r="M38" s="39" t="s">
+        <v>286</v>
+      </c>
+      <c r="N38" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="O38" s="39" t="s">
+        <v>486</v>
+      </c>
+      <c r="P38" s="39" t="s">
+        <v>814</v>
+      </c>
+      <c r="Q38" s="39" t="s">
+        <v>869</v>
+      </c>
+      <c r="R38" s="39" t="s">
+        <v>628</v>
+      </c>
+      <c r="S38" s="39" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="27">
+      <c r="K39" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="L39" s="39"/>
+      <c r="M39" s="39" t="s">
+        <v>294</v>
+      </c>
+      <c r="N39" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="O39" s="39" t="s">
+        <v>495</v>
+      </c>
+      <c r="P39" s="39" t="s">
+        <v>815</v>
+      </c>
+      <c r="Q39" s="39" t="s">
+        <v>878</v>
+      </c>
+      <c r="R39" s="39" t="s">
+        <v>637</v>
+      </c>
+      <c r="S39" s="39" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="27">
+      <c r="K40" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="L40" s="39"/>
+      <c r="M40" s="39" t="s">
+        <v>302</v>
+      </c>
+      <c r="N40" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="O40" s="39" t="s">
+        <v>503</v>
+      </c>
+      <c r="P40" s="39" t="s">
+        <v>816</v>
+      </c>
+      <c r="Q40" s="39" t="s">
+        <v>886</v>
+      </c>
+      <c r="R40" s="39" t="s">
+        <v>646</v>
+      </c>
+      <c r="S40" s="39" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="27">
+      <c r="K41" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="L41" s="39"/>
+      <c r="M41" s="39" t="s">
+        <v>310</v>
+      </c>
+      <c r="N41" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="O41" s="39" t="s">
+        <v>512</v>
+      </c>
+      <c r="P41" s="39" t="s">
+        <v>817</v>
+      </c>
+      <c r="Q41" s="39" t="s">
+        <v>895</v>
+      </c>
+      <c r="R41" s="39" t="s">
+        <v>655</v>
+      </c>
+      <c r="S41" s="39" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="27">
+      <c r="K42" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="L42" s="39"/>
+      <c r="M42" s="39" t="s">
+        <v>318</v>
+      </c>
+      <c r="N42" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="O42" s="39" t="s">
+        <v>521</v>
+      </c>
+      <c r="P42" s="39" t="s">
+        <v>818</v>
+      </c>
+      <c r="Q42" s="39" t="s">
+        <v>904</v>
+      </c>
+      <c r="R42" s="39" t="s">
+        <v>664</v>
+      </c>
+      <c r="S42" s="39" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="27">
+      <c r="K43" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="L43" s="39"/>
+      <c r="M43" s="39" t="s">
+        <v>326</v>
+      </c>
+      <c r="N43" s="39" t="s">
+        <v>137</v>
+      </c>
+      <c r="O43" s="39" t="s">
+        <v>530</v>
+      </c>
+      <c r="P43" s="39" t="s">
+        <v>819</v>
+      </c>
+      <c r="Q43" s="39" t="s">
+        <v>913</v>
+      </c>
+      <c r="R43" s="39" t="s">
+        <v>673</v>
+      </c>
+      <c r="S43" s="39" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="27">
+      <c r="K44" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="L44" s="39"/>
+      <c r="M44" s="39" t="s">
+        <v>334</v>
+      </c>
+      <c r="N44" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="O44" s="39"/>
+      <c r="P44" s="39"/>
+      <c r="Q44" s="39"/>
+      <c r="R44" s="39"/>
+      <c r="S44" s="39" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" ht="27">
+      <c r="K45" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="39"/>
+      <c r="M45" s="39" t="s">
+        <v>342</v>
+      </c>
+      <c r="N45" s="39" t="s">
+        <v>153</v>
+      </c>
+      <c r="O45" s="39"/>
+      <c r="P45" s="39"/>
+      <c r="Q45" s="39"/>
+      <c r="R45" s="39"/>
+      <c r="S45" s="39" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" ht="27">
+      <c r="K46" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="L46" s="39"/>
+      <c r="M46" s="39" t="s">
+        <v>350</v>
+      </c>
+      <c r="N46" s="39" t="s">
+        <v>161</v>
+      </c>
+      <c r="O46" s="39"/>
+      <c r="P46" s="39"/>
+      <c r="Q46" s="39"/>
+      <c r="R46" s="39"/>
+      <c r="S46" s="39" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" ht="27">
+      <c r="K47" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="L47" s="39"/>
+      <c r="M47" s="39" t="s">
+        <v>358</v>
+      </c>
+      <c r="N47" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="O47" s="39"/>
+      <c r="P47" s="39"/>
+      <c r="Q47" s="39"/>
+      <c r="R47" s="39"/>
+      <c r="S47" s="39" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" ht="27">
+      <c r="K48" s="43" t="s">
+        <v>11</v>
+      </c>
+      <c r="L48" s="39"/>
+      <c r="M48" s="39" t="s">
+        <v>366</v>
+      </c>
+      <c r="N48" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="O48" s="39"/>
+      <c r="P48" s="39"/>
+      <c r="Q48" s="39"/>
+      <c r="R48" s="39"/>
+      <c r="S48" s="39" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="49" spans="11:19" ht="27">
+      <c r="K49" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="L49" s="39"/>
+      <c r="M49" s="39" t="s">
+        <v>374</v>
+      </c>
+      <c r="N49" s="39" t="s">
+        <v>185</v>
+      </c>
+      <c r="O49" s="39"/>
+      <c r="P49" s="39"/>
+      <c r="Q49" s="39"/>
+      <c r="R49" s="39"/>
+      <c r="S49" s="39" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="50" spans="11:19" ht="27">
+      <c r="K50" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="L50" s="39" t="s">
+        <v>1300</v>
+      </c>
+      <c r="M50" s="39" t="s">
+        <v>382</v>
+      </c>
+      <c r="N50" s="39"/>
+      <c r="O50" s="39" t="s">
+        <v>539</v>
+      </c>
+      <c r="P50" s="39"/>
+      <c r="Q50" s="39"/>
+      <c r="R50" s="39" t="s">
+        <v>682</v>
+      </c>
+      <c r="S50" s="39"/>
+    </row>
+    <row r="51" spans="11:19" ht="27">
+      <c r="K51" s="43" t="s">
+        <v>193</v>
+      </c>
+      <c r="L51" s="39"/>
+      <c r="M51" s="39"/>
+      <c r="N51" s="39" t="s">
+        <v>194</v>
+      </c>
+      <c r="O51" s="39"/>
+      <c r="P51" s="39"/>
+      <c r="Q51" s="39" t="s">
+        <v>922</v>
+      </c>
+      <c r="R51" s="39"/>
+      <c r="S51" s="39"/>
+    </row>
+    <row r="52" spans="11:19" ht="27">
+      <c r="K52" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="L52" s="39" t="s">
+        <v>1316</v>
+      </c>
+      <c r="M52" s="39" t="s">
+        <v>390</v>
+      </c>
+      <c r="N52" s="39" t="s">
+        <v>202</v>
+      </c>
+      <c r="O52" s="39" t="s">
+        <v>548</v>
+      </c>
+      <c r="P52" s="39"/>
+      <c r="Q52" s="39" t="s">
+        <v>931</v>
+      </c>
+      <c r="R52" s="39" t="s">
+        <v>691</v>
+      </c>
+      <c r="S52" s="39" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="53" spans="11:19" ht="14.5" thickBot="1">
+      <c r="K53" s="44" t="s">
+        <v>15</v>
+      </c>
+      <c r="L53" s="41" t="s">
+        <v>474</v>
+      </c>
+      <c r="M53" s="41" t="s">
+        <v>398</v>
+      </c>
+      <c r="N53" s="41" t="s">
+        <v>210</v>
+      </c>
+      <c r="O53" s="41" t="s">
+        <v>557</v>
+      </c>
+      <c r="P53" s="41" t="s">
+        <v>706</v>
+      </c>
+      <c r="Q53" s="41" t="s">
+        <v>940</v>
+      </c>
+      <c r="R53" s="41" t="s">
+        <v>700</v>
+      </c>
+      <c r="S53" s="41">
+        <v>0.61699999999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="11:19" ht="14.5" thickTop="1">
+      <c r="K54" s="43"/>
+      <c r="L54" s="39"/>
+      <c r="M54" s="39"/>
+      <c r="N54" s="40"/>
+      <c r="O54" s="40"/>
+      <c r="P54" s="40"/>
+      <c r="Q54" s="40"/>
+      <c r="R54" s="39"/>
+    </row>
+    <row r="55" spans="11:19">
+      <c r="K55" s="43"/>
+      <c r="L55" s="39"/>
+      <c r="M55" s="39"/>
+      <c r="N55" s="40"/>
+      <c r="O55" s="40"/>
+      <c r="P55" s="40"/>
+      <c r="Q55" s="40"/>
+      <c r="R55" s="39"/>
+    </row>
+    <row r="56" spans="11:19">
+      <c r="K56" s="43"/>
+      <c r="L56" s="39"/>
+      <c r="M56" s="39"/>
+      <c r="N56" s="40"/>
+      <c r="O56" s="40"/>
+      <c r="P56" s="40"/>
+      <c r="Q56" s="40"/>
+      <c r="R56" s="39"/>
+    </row>
+    <row r="57" spans="11:19">
+      <c r="K57" s="43"/>
+      <c r="L57" s="39"/>
+      <c r="M57" s="39"/>
+      <c r="N57" s="40"/>
+      <c r="O57" s="40"/>
+      <c r="P57" s="40"/>
+      <c r="Q57" s="40"/>
+      <c r="R57" s="39"/>
+    </row>
+    <row r="58" spans="11:19">
+      <c r="K58" s="43"/>
+      <c r="L58" s="39"/>
+      <c r="M58" s="39"/>
+      <c r="N58" s="40"/>
+      <c r="O58" s="40"/>
+      <c r="P58" s="40"/>
+      <c r="Q58" s="40"/>
+      <c r="R58" s="39"/>
+    </row>
+    <row r="59" spans="11:19">
+      <c r="K59" s="43"/>
+      <c r="L59" s="39"/>
+      <c r="M59" s="39"/>
+      <c r="N59" s="40"/>
+      <c r="O59" s="40"/>
+      <c r="P59" s="40"/>
+      <c r="Q59" s="40"/>
+      <c r="R59" s="39"/>
+    </row>
+    <row r="60" spans="11:19">
+      <c r="K60" s="43"/>
+      <c r="L60" s="39"/>
+      <c r="M60" s="39"/>
+      <c r="N60" s="40"/>
+      <c r="O60" s="40"/>
+      <c r="P60" s="40"/>
+      <c r="Q60" s="40"/>
+      <c r="R60" s="39"/>
+    </row>
+    <row r="61" spans="11:19">
+      <c r="K61" s="43"/>
+      <c r="L61" s="39"/>
+      <c r="M61" s="39"/>
+      <c r="N61" s="40"/>
+      <c r="O61" s="40"/>
+      <c r="P61" s="40"/>
+      <c r="Q61" s="40"/>
+      <c r="R61" s="39"/>
+    </row>
+    <row r="62" spans="11:19">
+      <c r="K62" s="43"/>
+      <c r="L62" s="39"/>
+      <c r="M62" s="39"/>
+      <c r="N62" s="40"/>
+      <c r="O62" s="40"/>
+      <c r="P62" s="40"/>
+      <c r="Q62" s="40"/>
+      <c r="R62" s="39"/>
+    </row>
+    <row r="63" spans="11:19">
+      <c r="K63" s="43"/>
+      <c r="L63" s="39"/>
+      <c r="M63" s="40"/>
+      <c r="N63" s="39"/>
+      <c r="O63" s="40"/>
+      <c r="P63" s="40"/>
+      <c r="Q63" s="39"/>
+      <c r="R63" s="39"/>
+      <c r="S63" s="1" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="64" spans="11:19">
+      <c r="K64" s="43"/>
+      <c r="L64" s="39"/>
+      <c r="M64" s="40"/>
+      <c r="N64" s="39"/>
+      <c r="O64" s="40"/>
+      <c r="P64" s="40"/>
+      <c r="Q64" s="39"/>
+      <c r="R64" s="39"/>
+    </row>
+    <row r="65" spans="11:18">
+      <c r="K65" s="43"/>
+      <c r="L65" s="40"/>
+      <c r="M65" s="39"/>
+      <c r="N65" s="40"/>
+      <c r="O65" s="40"/>
+      <c r="P65" s="39"/>
+      <c r="Q65" s="40"/>
+      <c r="R65" s="39"/>
+    </row>
+    <row r="66" spans="11:18">
+      <c r="K66" s="43"/>
+      <c r="L66" s="40"/>
+      <c r="M66" s="39"/>
+      <c r="N66" s="40"/>
+      <c r="O66" s="40"/>
+      <c r="P66" s="39"/>
+      <c r="Q66" s="40"/>
+      <c r="R66" s="39"/>
+    </row>
+    <row r="67" spans="11:18">
+      <c r="K67" s="43"/>
+      <c r="L67" s="39"/>
+      <c r="M67" s="39"/>
+      <c r="N67" s="39"/>
+      <c r="O67" s="40"/>
+      <c r="P67" s="39"/>
+      <c r="Q67" s="39"/>
+      <c r="R67" s="39"/>
+    </row>
+    <row r="68" spans="11:18">
+      <c r="K68" s="43"/>
+      <c r="L68" s="39"/>
+      <c r="M68" s="39"/>
+      <c r="N68" s="39"/>
+      <c r="O68" s="40"/>
+      <c r="P68" s="39"/>
+      <c r="Q68" s="39"/>
+      <c r="R68" s="39"/>
+    </row>
+    <row r="69" spans="11:18" ht="14.5" thickBot="1">
+      <c r="K69" s="44"/>
+      <c r="L69" s="41"/>
+      <c r="M69" s="41"/>
+      <c r="N69" s="41"/>
+      <c r="O69" s="41"/>
+      <c r="P69" s="41"/>
+      <c r="Q69" s="41"/>
+      <c r="R69" s="41"/>
+    </row>
+    <row r="70" spans="11:18" ht="14.5" thickTop="1"/>
   </sheetData>
-  <mergeCells count="48">
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{460ADBCF-DD64-43BA-8639-7EE07046B667}">
+  <dimension ref="A1:H20"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" style="23" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" style="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="14.5" thickBot="1"/>
+    <row r="2" spans="1:8" ht="14.5" thickTop="1">
+      <c r="A2" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>618</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>1277</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>988</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>709</v>
+      </c>
+      <c r="H2" s="26" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="27">
+      <c r="A3" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>813</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>860</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>619</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="27">
+      <c r="A4" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>486</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>814</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>869</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>628</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="27">
+      <c r="A5" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>495</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>815</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>878</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>637</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="27">
+      <c r="A6" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>503</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>816</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>886</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>646</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="27">
+      <c r="A7" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>310</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>512</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>817</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>895</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>655</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="27">
+      <c r="A8" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>818</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>904</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>664</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="40.5">
+      <c r="A9" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>530</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>819</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>913</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>673</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="27">
+      <c r="A10" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="27"/>
+    </row>
+    <row r="11" spans="1:8" ht="27">
+      <c r="A11" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>342</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="27"/>
+    </row>
+    <row r="12" spans="1:8" ht="27">
+      <c r="A12" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>350</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="27"/>
+    </row>
+    <row r="13" spans="1:8" ht="27">
+      <c r="A13" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>358</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="27"/>
+    </row>
+    <row r="14" spans="1:8" ht="27">
+      <c r="A14" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>366</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="27"/>
+    </row>
+    <row r="15" spans="1:8" ht="27">
+      <c r="A15" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="27"/>
+    </row>
+    <row r="16" spans="1:8" ht="27">
+      <c r="A16" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>382</v>
+      </c>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16" t="s">
+        <v>539</v>
+      </c>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="16" t="s">
+        <v>682</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="27">
+      <c r="A17" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="D17" s="16"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="17" t="s">
+        <v>922</v>
+      </c>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+    </row>
+    <row r="18" spans="1:8" ht="40.5">
+      <c r="A18" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>548</v>
+      </c>
+      <c r="E18" s="18"/>
+      <c r="F18" s="17" t="s">
+        <v>931</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>691</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="14.5" thickBot="1">
+      <c r="A19" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>398</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>557</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>706</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>940</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>700</v>
+      </c>
+      <c r="H19" s="21" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="14.5" thickTop="1"/>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>